--- a/Predicciones mundial 2026 (Respuestas).xlsx
+++ b/Predicciones mundial 2026 (Respuestas).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-4°1°\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC05B47-161A-471F-ABFE-8DC059608A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA28643-0E29-42AE-8C0D-9BAADAC2F7F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="165">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -681,5205 +681,506 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="747">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
+  <dxfs count="77">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -5903,7 +1204,28 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF5B3F86"/>
+          <bgColor rgb="FF5B3F86"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border>
@@ -5921,37 +1243,13 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF5B3F86"/>
-          <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="743"/>
-      <tableStyleElement type="headerRow" dxfId="746"/>
-      <tableStyleElement type="firstRowStripe" dxfId="745"/>
-      <tableStyleElement type="secondRowStripe" dxfId="744"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="76"/>
+      <tableStyleElement type="headerRow" dxfId="75"/>
+      <tableStyleElement type="firstRowStripe" dxfId="74"/>
+      <tableStyleElement type="secondRowStripe" dxfId="73"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -6043,10 +1341,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="741">
+    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="72">
       <calculatedColumnFormula array="1">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="742">
+    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="71">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6779,7 +2077,7 @@
       </c>
       <c r="BX2" s="5" cm="1">
         <f t="array" ref="BX2">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7014,7 +2312,7 @@
       </c>
       <c r="BX3" s="5" cm="1">
         <f t="array" ref="BX3">SUMPRODUCT((D3:BW3=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7249,7 +2547,7 @@
       </c>
       <c r="BX4" s="5" cm="1">
         <f t="array" ref="BX4">SUMPRODUCT((D4:BW4=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7484,7 +2782,7 @@
       </c>
       <c r="BX5" s="5" cm="1">
         <f t="array" ref="BX5">SUMPRODUCT((D5:BW5=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7719,7 +3017,7 @@
       </c>
       <c r="BX6" s="5" cm="1">
         <f t="array" ref="BX6">SUMPRODUCT((D6:BW6=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -8189,7 +3487,7 @@
       </c>
       <c r="BX8" s="5" cm="1">
         <f t="array" ref="BX8">SUMPRODUCT((D8:BW8=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -8424,7 +3722,7 @@
       </c>
       <c r="BX9" s="5" cm="1">
         <f t="array" ref="BX9">SUMPRODUCT((D9:BW9=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -8659,7 +3957,7 @@
       </c>
       <c r="BX10" s="5" cm="1">
         <f t="array" ref="BX10">SUMPRODUCT((D10:BW10=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -8894,7 +4192,7 @@
       </c>
       <c r="BX11" s="5" cm="1">
         <f t="array" ref="BX11">SUMPRODUCT((D11:BW11=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -9129,7 +4427,7 @@
       </c>
       <c r="BX12" s="5" cm="1">
         <f t="array" ref="BX12">SUMPRODUCT((D12:BW12=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -9364,7 +4662,7 @@
       </c>
       <c r="BX13" s="5" cm="1">
         <f t="array" ref="BX13">SUMPRODUCT((D13:BW13=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -9599,7 +4897,7 @@
       </c>
       <c r="BX14" s="5" cm="1">
         <f t="array" ref="BX14">SUMPRODUCT((D14:BW14=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -10069,7 +5367,7 @@
       </c>
       <c r="BX16" s="5" cm="1">
         <f t="array" ref="BX16">SUMPRODUCT((D16:BW16=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY16" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -10304,7 +5602,7 @@
       </c>
       <c r="BX17" s="5" cm="1">
         <f t="array" ref="BX17">SUMPRODUCT((D17:BW17=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BY17" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -10539,7 +5837,7 @@
       </c>
       <c r="BX18" s="5" cm="1">
         <f t="array" ref="BX18">SUMPRODUCT((D18:BW18=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BY18" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -10774,7 +6072,7 @@
       </c>
       <c r="BX19" s="5" cm="1">
         <f t="array" ref="BX19">SUMPRODUCT((D19:BW19=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY19" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -10854,6 +6152,9 @@
       <c r="AJ21" s="6" t="s">
         <v>91</v>
       </c>
+      <c r="AK21" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="AN21" s="6" t="s">
         <v>81</v>
       </c>
@@ -10893,181 +6194,186 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D19">
-    <cfRule type="cellIs" dxfId="68" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="40" operator="equal">
       <formula>$D$21</formula>
     </cfRule>
-    <cfRule type="expression" priority="38">
+    <cfRule type="expression" priority="39">
       <formula>$D$22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E19">
-    <cfRule type="cellIs" dxfId="67" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="38" operator="equal">
       <formula>$E$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F19">
-    <cfRule type="cellIs" dxfId="66" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="37" operator="equal">
       <formula>$F$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G19">
-    <cfRule type="cellIs" dxfId="65" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="36" operator="equal">
       <formula>$G$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J19">
-    <cfRule type="cellIs" dxfId="64" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="35" operator="equal">
       <formula>$J$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K19">
-    <cfRule type="cellIs" dxfId="63" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="34" operator="equal">
       <formula>$K$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L19">
-    <cfRule type="cellIs" dxfId="62" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="33" operator="equal">
       <formula>$L$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M19">
-    <cfRule type="cellIs" dxfId="61" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="32" operator="equal">
       <formula>$M$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P19">
-    <cfRule type="cellIs" dxfId="60" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="31" operator="equal">
       <formula>$P$21</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S19">
-    <cfRule type="cellIs" dxfId="59" priority="29" operator="equal">
-      <formula>$S$21</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q19">
-    <cfRule type="cellIs" dxfId="58" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="29" operator="equal">
       <formula>$Q$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R19">
-    <cfRule type="cellIs" dxfId="57" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="28" operator="equal">
       <formula>$R$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S19">
+    <cfRule type="cellIs" dxfId="59" priority="30" operator="equal">
+      <formula>$S$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="V2:V19">
-    <cfRule type="cellIs" dxfId="56" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="27" operator="equal">
       <formula>$V$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W19">
-    <cfRule type="cellIs" dxfId="55" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="26" operator="equal">
       <formula>$W$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X19">
-    <cfRule type="cellIs" dxfId="54" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="25" operator="equal">
       <formula>$X$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y19">
-    <cfRule type="cellIs" dxfId="53" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="24" operator="equal">
       <formula>$Y$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB19">
-    <cfRule type="cellIs" dxfId="52" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="21" operator="equal">
       <formula>$AB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC19">
-    <cfRule type="cellIs" dxfId="51" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="20" operator="equal">
       <formula>$AC$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD19">
-    <cfRule type="cellIs" dxfId="50" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="19" operator="equal">
       <formula>$AD$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE19">
-    <cfRule type="cellIs" dxfId="49" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="18" operator="equal">
       <formula>$AE$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH19">
-    <cfRule type="cellIs" dxfId="48" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="17" operator="equal">
       <formula>$AH$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI19">
-    <cfRule type="cellIs" dxfId="47" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="16" operator="equal">
       <formula>$AI$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ19">
-    <cfRule type="cellIs" dxfId="46" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="15" operator="equal">
       <formula>$AJ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN19">
-    <cfRule type="cellIs" dxfId="45" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="14" operator="equal">
       <formula>$AN$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO19">
-    <cfRule type="cellIs" dxfId="44" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="13" operator="equal">
       <formula>$AO$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT19">
-    <cfRule type="cellIs" dxfId="43" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="12" operator="equal">
       <formula>$AT$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU19">
-    <cfRule type="cellIs" dxfId="42" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="11" operator="equal">
       <formula>$AU$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ19">
-    <cfRule type="cellIs" dxfId="41" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="10" operator="equal">
       <formula>$AZ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA19">
-    <cfRule type="cellIs" dxfId="40" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="8" operator="equal">
       <formula>$BA$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF19">
-    <cfRule type="cellIs" dxfId="39" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="7" operator="equal">
       <formula>$BF$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG19">
-    <cfRule type="cellIs" dxfId="38" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="6" operator="equal">
       <formula>$BG$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL19">
-    <cfRule type="cellIs" dxfId="37" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="5" operator="equal">
       <formula>$BL$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM19">
-    <cfRule type="cellIs" dxfId="36" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="4" operator="equal">
       <formula>$BM$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR19">
-    <cfRule type="cellIs" dxfId="35" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="3" operator="equal">
       <formula>$BR$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS19">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="equal">
+      <formula>$BS$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK2:AK19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$BS$21</formula>
+      <formula>$AK$21</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Predicciones mundial 2026 (Respuestas).xlsx
+++ b/Predicciones mundial 2026 (Respuestas).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-4°1°\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA28643-0E29-42AE-8C0D-9BAADAC2F7F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45EBD486-BAA4-4829-9C08-796257E1580F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -537,15 +537,9 @@
     <t>yagosayas09@gmail.com</t>
   </si>
   <si>
-    <t>yago sayas</t>
-  </si>
-  <si>
     <t>valentinorussosuarez@gmail.com</t>
   </si>
   <si>
-    <t>Russo Suarez Valentino</t>
-  </si>
-  <si>
     <t>Túnez</t>
   </si>
   <si>
@@ -558,15 +552,9 @@
     <t>ianfind38@gmail.com</t>
   </si>
   <si>
-    <t>Ian el papi Findlay</t>
-  </si>
-  <si>
     <t>daniloyxr33@gmail.com</t>
   </si>
   <si>
-    <t>Giacobini danilo</t>
-  </si>
-  <si>
     <t>Haití</t>
   </si>
   <si>
@@ -586,6 +574,18 @@
   </si>
   <si>
     <t>Respuestas</t>
+  </si>
+  <si>
+    <t>Yago Sayas</t>
+  </si>
+  <si>
+    <t>Ian Findlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valentino Russo Suarez </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danilo Giacobini </t>
   </si>
 </sst>
 </file>
@@ -681,252 +681,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="77">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="42">
     <dxf>
       <fill>
         <patternFill>
@@ -1246,10 +1001,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="76"/>
-      <tableStyleElement type="headerRow" dxfId="75"/>
-      <tableStyleElement type="firstRowStripe" dxfId="74"/>
-      <tableStyleElement type="secondRowStripe" dxfId="73"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="41"/>
+      <tableStyleElement type="headerRow" dxfId="40"/>
+      <tableStyleElement type="firstRowStripe" dxfId="39"/>
+      <tableStyleElement type="secondRowStripe" dxfId="38"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1341,10 +1096,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="72">
+    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="37">
       <calculatedColumnFormula array="1">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="71">
+    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="36">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1843,10 +1598,10 @@
         <v>74</v>
       </c>
       <c r="BX1" s="4" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="BY1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:77" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1857,7 +1612,7 @@
         <v>75</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>76</v>
@@ -4677,7 +4432,7 @@
         <v>147</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>112</v>
@@ -4901,7 +4656,7 @@
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
-        <v>yago sayas</v>
+        <v>Yago Sayas</v>
       </c>
     </row>
     <row r="15" spans="1:77" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4909,10 +4664,10 @@
         <v>46183.849086759263</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>112</v>
@@ -5014,7 +4769,7 @@
         <v>90</v>
       </c>
       <c r="AK15" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AL15" s="3" t="s">
         <v>81</v>
@@ -5136,7 +4891,7 @@
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
-        <v>Russo Suarez Valentino</v>
+        <v xml:space="preserve">Valentino Russo Suarez </v>
       </c>
     </row>
     <row r="16" spans="1:77" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5144,10 +4899,10 @@
         <v>46183.879928333336</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>112</v>
@@ -5379,10 +5134,10 @@
         <v>46183.921634039347</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>76</v>
@@ -5606,7 +5361,7 @@
       </c>
       <c r="BY17" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
-        <v>Ian el papi Findlay</v>
+        <v>Ian Findlay</v>
       </c>
     </row>
     <row r="18" spans="1:77" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5614,10 +5369,10 @@
         <v>46184.371469907404</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>76</v>
@@ -5659,7 +5414,7 @@
         <v>83</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>83</v>
@@ -5841,7 +5596,7 @@
       </c>
       <c r="BY18" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
-        <v>Giacobini danilo</v>
+        <v xml:space="preserve">Danilo Giacobini </v>
       </c>
     </row>
     <row r="19" spans="1:77" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5849,10 +5604,10 @@
         <v>46184.451000555557</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>112</v>
@@ -6081,7 +5836,7 @@
     </row>
     <row r="21" spans="1:77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>112</v>
@@ -6194,7 +5949,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D19">
-    <cfRule type="cellIs" dxfId="70" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="40" operator="equal">
       <formula>$D$21</formula>
     </cfRule>
     <cfRule type="expression" priority="39">
@@ -6202,178 +5957,178 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E19">
-    <cfRule type="cellIs" dxfId="69" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="38" operator="equal">
       <formula>$E$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F19">
-    <cfRule type="cellIs" dxfId="68" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="37" operator="equal">
       <formula>$F$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G19">
-    <cfRule type="cellIs" dxfId="67" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="36" operator="equal">
       <formula>$G$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J19">
-    <cfRule type="cellIs" dxfId="66" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="35" operator="equal">
       <formula>$J$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K19">
-    <cfRule type="cellIs" dxfId="65" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="34" operator="equal">
       <formula>$K$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L19">
-    <cfRule type="cellIs" dxfId="64" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="33" operator="equal">
       <formula>$L$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M19">
-    <cfRule type="cellIs" dxfId="63" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="32" operator="equal">
       <formula>$M$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P19">
-    <cfRule type="cellIs" dxfId="62" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="31" operator="equal">
       <formula>$P$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q19">
-    <cfRule type="cellIs" dxfId="61" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="29" operator="equal">
       <formula>$Q$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R19">
-    <cfRule type="cellIs" dxfId="60" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="28" operator="equal">
       <formula>$R$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S19">
-    <cfRule type="cellIs" dxfId="59" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="30" operator="equal">
       <formula>$S$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V19">
-    <cfRule type="cellIs" dxfId="58" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="27" operator="equal">
       <formula>$V$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W19">
-    <cfRule type="cellIs" dxfId="57" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="26" operator="equal">
       <formula>$W$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X19">
-    <cfRule type="cellIs" dxfId="56" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="25" operator="equal">
       <formula>$X$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y19">
-    <cfRule type="cellIs" dxfId="55" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="24" operator="equal">
       <formula>$Y$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB19">
-    <cfRule type="cellIs" dxfId="54" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="21" operator="equal">
       <formula>$AB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC19">
-    <cfRule type="cellIs" dxfId="53" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="20" operator="equal">
       <formula>$AC$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD19">
-    <cfRule type="cellIs" dxfId="52" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
       <formula>$AD$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE19">
-    <cfRule type="cellIs" dxfId="51" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
       <formula>$AE$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH19">
-    <cfRule type="cellIs" dxfId="50" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="17" operator="equal">
       <formula>$AH$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI19">
-    <cfRule type="cellIs" dxfId="49" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
       <formula>$AI$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ19">
-    <cfRule type="cellIs" dxfId="48" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
       <formula>$AJ$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AK2:AK19">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+      <formula>$AK$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN19">
-    <cfRule type="cellIs" dxfId="47" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
       <formula>$AN$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO19">
-    <cfRule type="cellIs" dxfId="46" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
       <formula>$AO$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT19">
-    <cfRule type="cellIs" dxfId="45" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
       <formula>$AT$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU19">
-    <cfRule type="cellIs" dxfId="44" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
       <formula>$AU$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ19">
-    <cfRule type="cellIs" dxfId="43" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
       <formula>$AZ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA19">
-    <cfRule type="cellIs" dxfId="42" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
       <formula>$BA$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF19">
-    <cfRule type="cellIs" dxfId="41" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>$BF$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG19">
-    <cfRule type="cellIs" dxfId="40" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>$BG$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL19">
-    <cfRule type="cellIs" dxfId="39" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>$BL$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM19">
-    <cfRule type="cellIs" dxfId="38" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>$BM$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR19">
-    <cfRule type="cellIs" dxfId="37" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>$BR$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS19">
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>$BS$21</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK2:AK19">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$AK$21</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Predicciones mundial 2026 (Respuestas).xlsx
+++ b/Predicciones mundial 2026 (Respuestas).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-4°1°\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45EBD486-BAA4-4829-9C08-796257E1580F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719F4449-AE8B-4FC0-99C3-AEAFF92A9BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="165">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -681,7 +681,266 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="42">
+  <dxfs count="79">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1001,10 +1260,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="41"/>
-      <tableStyleElement type="headerRow" dxfId="40"/>
-      <tableStyleElement type="firstRowStripe" dxfId="39"/>
-      <tableStyleElement type="secondRowStripe" dxfId="38"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="78"/>
+      <tableStyleElement type="headerRow" dxfId="77"/>
+      <tableStyleElement type="firstRowStripe" dxfId="76"/>
+      <tableStyleElement type="secondRowStripe" dxfId="75"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1096,10 +1355,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="37">
+    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="74">
       <calculatedColumnFormula array="1">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="36">
+    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="73">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1832,7 +2091,7 @@
       </c>
       <c r="BX2" s="5" cm="1">
         <f t="array" ref="BX2">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2067,7 +2326,7 @@
       </c>
       <c r="BX3" s="5" cm="1">
         <f t="array" ref="BX3">SUMPRODUCT((D3:BW3=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2302,7 +2561,7 @@
       </c>
       <c r="BX4" s="5" cm="1">
         <f t="array" ref="BX4">SUMPRODUCT((D4:BW4=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2537,7 +2796,7 @@
       </c>
       <c r="BX5" s="5" cm="1">
         <f t="array" ref="BX5">SUMPRODUCT((D5:BW5=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2772,7 +3031,7 @@
       </c>
       <c r="BX6" s="5" cm="1">
         <f t="array" ref="BX6">SUMPRODUCT((D6:BW6=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3007,7 +3266,7 @@
       </c>
       <c r="BX7" s="5" cm="1">
         <f t="array" ref="BX7">SUMPRODUCT((D7:BW7=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3242,7 +3501,7 @@
       </c>
       <c r="BX8" s="5" cm="1">
         <f t="array" ref="BX8">SUMPRODUCT((D8:BW8=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3477,7 +3736,7 @@
       </c>
       <c r="BX9" s="5" cm="1">
         <f t="array" ref="BX9">SUMPRODUCT((D9:BW9=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3712,7 +3971,7 @@
       </c>
       <c r="BX10" s="5" cm="1">
         <f t="array" ref="BX10">SUMPRODUCT((D10:BW10=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3947,7 +4206,7 @@
       </c>
       <c r="BX11" s="5" cm="1">
         <f t="array" ref="BX11">SUMPRODUCT((D11:BW11=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4182,7 +4441,7 @@
       </c>
       <c r="BX12" s="5" cm="1">
         <f t="array" ref="BX12">SUMPRODUCT((D12:BW12=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4417,7 +4676,7 @@
       </c>
       <c r="BX13" s="5" cm="1">
         <f t="array" ref="BX13">SUMPRODUCT((D13:BW13=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4652,7 +4911,7 @@
       </c>
       <c r="BX14" s="5" cm="1">
         <f t="array" ref="BX14">SUMPRODUCT((D14:BW14=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4887,7 +5146,7 @@
       </c>
       <c r="BX15" s="5" cm="1">
         <f t="array" ref="BX15">SUMPRODUCT((D15:BW15=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5122,7 +5381,7 @@
       </c>
       <c r="BX16" s="5" cm="1">
         <f t="array" ref="BX16">SUMPRODUCT((D16:BW16=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY16" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5357,7 +5616,7 @@
       </c>
       <c r="BX17" s="5" cm="1">
         <f t="array" ref="BX17">SUMPRODUCT((D17:BW17=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BY17" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5592,7 +5851,7 @@
       </c>
       <c r="BX18" s="5" cm="1">
         <f t="array" ref="BX18">SUMPRODUCT((D18:BW18=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BY18" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5827,7 +6086,7 @@
       </c>
       <c r="BX19" s="5" cm="1">
         <f t="array" ref="BX19">SUMPRODUCT((D19:BW19=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY19" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5922,6 +6181,9 @@
       <c r="AU21" s="6" t="s">
         <v>81</v>
       </c>
+      <c r="AV21" t="s">
+        <v>95</v>
+      </c>
       <c r="AZ21" s="6" t="s">
         <v>98</v>
       </c>
@@ -5949,186 +6211,191 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D19">
-    <cfRule type="cellIs" dxfId="35" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="41" operator="equal">
       <formula>$D$21</formula>
     </cfRule>
-    <cfRule type="expression" priority="39">
+    <cfRule type="expression" priority="40">
       <formula>$D$22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E19">
-    <cfRule type="cellIs" dxfId="34" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="39" operator="equal">
       <formula>$E$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F19">
-    <cfRule type="cellIs" dxfId="33" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="38" operator="equal">
       <formula>$F$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G19">
-    <cfRule type="cellIs" dxfId="32" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="37" operator="equal">
       <formula>$G$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J19">
-    <cfRule type="cellIs" dxfId="31" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="36" operator="equal">
       <formula>$J$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K19">
-    <cfRule type="cellIs" dxfId="30" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="35" operator="equal">
       <formula>$K$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L19">
-    <cfRule type="cellIs" dxfId="29" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="34" operator="equal">
       <formula>$L$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M19">
-    <cfRule type="cellIs" dxfId="28" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="33" operator="equal">
       <formula>$M$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P19">
-    <cfRule type="cellIs" dxfId="27" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="32" operator="equal">
       <formula>$P$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q19">
-    <cfRule type="cellIs" dxfId="26" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="30" operator="equal">
       <formula>$Q$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R19">
-    <cfRule type="cellIs" dxfId="25" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="29" operator="equal">
       <formula>$R$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S19">
-    <cfRule type="cellIs" dxfId="24" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="31" operator="equal">
       <formula>$S$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V19">
-    <cfRule type="cellIs" dxfId="23" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="28" operator="equal">
       <formula>$V$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W19">
-    <cfRule type="cellIs" dxfId="22" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="27" operator="equal">
       <formula>$W$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X19">
-    <cfRule type="cellIs" dxfId="21" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="26" operator="equal">
       <formula>$X$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y19">
-    <cfRule type="cellIs" dxfId="20" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="25" operator="equal">
       <formula>$Y$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB19">
-    <cfRule type="cellIs" dxfId="19" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="22" operator="equal">
       <formula>$AB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC19">
-    <cfRule type="cellIs" dxfId="18" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="21" operator="equal">
       <formula>$AC$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD19">
-    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="20" operator="equal">
       <formula>$AD$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE19">
-    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="19" operator="equal">
       <formula>$AE$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH19">
-    <cfRule type="cellIs" dxfId="15" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="18" operator="equal">
       <formula>$AH$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI19">
-    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="17" operator="equal">
       <formula>$AI$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ19">
-    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="16" operator="equal">
       <formula>$AJ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK19">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="2" operator="equal">
       <formula>$AK$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN19">
-    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="15" operator="equal">
       <formula>$AN$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO19">
-    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="14" operator="equal">
       <formula>$AO$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT19">
-    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="13" operator="equal">
       <formula>$AT$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU19">
-    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="12" operator="equal">
       <formula>$AU$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ19">
-    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="11" operator="equal">
       <formula>$AZ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA19">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="9" operator="equal">
       <formula>$BA$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF19">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="8" operator="equal">
       <formula>$BF$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG19">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="7" operator="equal">
       <formula>$BG$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL19">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="6" operator="equal">
       <formula>$BL$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM19">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="5" operator="equal">
       <formula>$BM$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR19">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="4" operator="equal">
       <formula>$BR$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS19">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="3" operator="equal">
       <formula>$BS$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AV2:AV19">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>$AV$21</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Predicciones mundial 2026 (Respuestas).xlsx
+++ b/Predicciones mundial 2026 (Respuestas).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-4°1°\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719F4449-AE8B-4FC0-99C3-AEAFF92A9BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACD96AF-5A60-4EE3-951A-C769E629C04B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="165">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -681,7 +681,294 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="79">
+  <dxfs count="120">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1260,10 +1547,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="78"/>
-      <tableStyleElement type="headerRow" dxfId="77"/>
-      <tableStyleElement type="firstRowStripe" dxfId="76"/>
-      <tableStyleElement type="secondRowStripe" dxfId="75"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="119"/>
+      <tableStyleElement type="headerRow" dxfId="118"/>
+      <tableStyleElement type="firstRowStripe" dxfId="117"/>
+      <tableStyleElement type="secondRowStripe" dxfId="116"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1355,10 +1642,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="74">
+    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="115">
       <calculatedColumnFormula array="1">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="73">
+    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="114">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2561,7 +2848,7 @@
       </c>
       <c r="BX4" s="5" cm="1">
         <f t="array" ref="BX4">SUMPRODUCT((D4:BW4=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3031,7 +3318,7 @@
       </c>
       <c r="BX6" s="5" cm="1">
         <f t="array" ref="BX6">SUMPRODUCT((D6:BW6=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3266,7 +3553,7 @@
       </c>
       <c r="BX7" s="5" cm="1">
         <f t="array" ref="BX7">SUMPRODUCT((D7:BW7=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4676,7 +4963,7 @@
       </c>
       <c r="BX13" s="5" cm="1">
         <f t="array" ref="BX13">SUMPRODUCT((D13:BW13=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6175,6 +6462,9 @@
       <c r="AO21" s="6" t="s">
         <v>81</v>
       </c>
+      <c r="AP21" s="6" t="s">
+        <v>81</v>
+      </c>
       <c r="AT21" s="6" t="s">
         <v>81</v>
       </c>
@@ -6183,6 +6473,9 @@
       </c>
       <c r="AV21" t="s">
         <v>95</v>
+      </c>
+      <c r="AW21" t="s">
+        <v>81</v>
       </c>
       <c r="AZ21" s="6" t="s">
         <v>98</v>
@@ -6211,191 +6504,201 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D19">
-    <cfRule type="cellIs" dxfId="72" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="43" operator="equal">
       <formula>$D$21</formula>
     </cfRule>
-    <cfRule type="expression" priority="40">
+    <cfRule type="expression" priority="42">
       <formula>$D$22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E19">
-    <cfRule type="cellIs" dxfId="71" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="41" operator="equal">
       <formula>$E$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F19">
-    <cfRule type="cellIs" dxfId="70" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="40" operator="equal">
       <formula>$F$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G19">
-    <cfRule type="cellIs" dxfId="69" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="39" operator="equal">
       <formula>$G$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J19">
-    <cfRule type="cellIs" dxfId="68" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="38" operator="equal">
       <formula>$J$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K19">
-    <cfRule type="cellIs" dxfId="67" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="37" operator="equal">
       <formula>$K$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L19">
-    <cfRule type="cellIs" dxfId="66" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="36" operator="equal">
       <formula>$L$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M19">
-    <cfRule type="cellIs" dxfId="65" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="35" operator="equal">
       <formula>$M$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P19">
-    <cfRule type="cellIs" dxfId="64" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="34" operator="equal">
       <formula>$P$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q19">
-    <cfRule type="cellIs" dxfId="63" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="32" operator="equal">
       <formula>$Q$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R19">
-    <cfRule type="cellIs" dxfId="62" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="31" operator="equal">
       <formula>$R$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S19">
-    <cfRule type="cellIs" dxfId="61" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="33" operator="equal">
       <formula>$S$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V19">
-    <cfRule type="cellIs" dxfId="60" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="30" operator="equal">
       <formula>$V$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W19">
-    <cfRule type="cellIs" dxfId="59" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="29" operator="equal">
       <formula>$W$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X19">
-    <cfRule type="cellIs" dxfId="58" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="28" operator="equal">
       <formula>$X$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y19">
-    <cfRule type="cellIs" dxfId="57" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="27" operator="equal">
       <formula>$Y$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB19">
-    <cfRule type="cellIs" dxfId="56" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="24" operator="equal">
       <formula>$AB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC19">
-    <cfRule type="cellIs" dxfId="55" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="23" operator="equal">
       <formula>$AC$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD19">
-    <cfRule type="cellIs" dxfId="54" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="22" operator="equal">
       <formula>$AD$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE19">
-    <cfRule type="cellIs" dxfId="53" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="21" operator="equal">
       <formula>$AE$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH19">
-    <cfRule type="cellIs" dxfId="52" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="20" operator="equal">
       <formula>$AH$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI19">
-    <cfRule type="cellIs" dxfId="51" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="19" operator="equal">
       <formula>$AI$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ19">
-    <cfRule type="cellIs" dxfId="50" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="18" operator="equal">
       <formula>$AJ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK19">
-    <cfRule type="cellIs" dxfId="49" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="4" operator="equal">
       <formula>$AK$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN19">
-    <cfRule type="cellIs" dxfId="48" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="17" operator="equal">
       <formula>$AN$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO19">
-    <cfRule type="cellIs" dxfId="47" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="16" operator="equal">
       <formula>$AO$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT19">
-    <cfRule type="cellIs" dxfId="46" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="15" operator="equal">
       <formula>$AT$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU19">
-    <cfRule type="cellIs" dxfId="45" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="14" operator="equal">
       <formula>$AU$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AV2:AV19">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+      <formula>$AV$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ19">
-    <cfRule type="cellIs" dxfId="44" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="13" operator="equal">
       <formula>$AZ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA19">
-    <cfRule type="cellIs" dxfId="43" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="11" operator="equal">
       <formula>$BA$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF19">
-    <cfRule type="cellIs" dxfId="42" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="10" operator="equal">
       <formula>$BF$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG19">
-    <cfRule type="cellIs" dxfId="41" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="9" operator="equal">
       <formula>$BG$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL19">
-    <cfRule type="cellIs" dxfId="40" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="8" operator="equal">
       <formula>$BL$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM19">
-    <cfRule type="cellIs" dxfId="39" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="7" operator="equal">
       <formula>$BM$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR19">
-    <cfRule type="cellIs" dxfId="38" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="6" operator="equal">
       <formula>$BR$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS19">
-    <cfRule type="cellIs" dxfId="37" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="5" operator="equal">
       <formula>$BS$21</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AV2:AV19">
+  <conditionalFormatting sqref="AW2:AW19">
+    <cfRule type="cellIs" dxfId="39" priority="2" operator="equal">
+      <formula>$AW$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP2:AP19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$AV$21</formula>
+      <formula>$AP$21</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Predicciones mundial 2026 (Respuestas).xlsx
+++ b/Predicciones mundial 2026 (Respuestas).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-4°1°\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACD96AF-5A60-4EE3-951A-C769E629C04B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B00C0CF7-0DB5-46E7-95AF-474224D3C500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="165">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -681,252 +681,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="120">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="85">
     <dxf>
       <fill>
         <patternFill>
@@ -1547,10 +1302,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="119"/>
-      <tableStyleElement type="headerRow" dxfId="118"/>
-      <tableStyleElement type="firstRowStripe" dxfId="117"/>
-      <tableStyleElement type="secondRowStripe" dxfId="116"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="84"/>
+      <tableStyleElement type="headerRow" dxfId="83"/>
+      <tableStyleElement type="firstRowStripe" dxfId="82"/>
+      <tableStyleElement type="secondRowStripe" dxfId="81"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1642,10 +1397,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="115">
+    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="80">
       <calculatedColumnFormula array="1">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="114">
+    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="79">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2378,7 +2133,7 @@
       </c>
       <c r="BX2" s="5" cm="1">
         <f t="array" ref="BX2">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2613,7 +2368,7 @@
       </c>
       <c r="BX3" s="5" cm="1">
         <f t="array" ref="BX3">SUMPRODUCT((D3:BW3=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2848,7 +2603,7 @@
       </c>
       <c r="BX4" s="5" cm="1">
         <f t="array" ref="BX4">SUMPRODUCT((D4:BW4=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3083,7 +2838,7 @@
       </c>
       <c r="BX5" s="5" cm="1">
         <f t="array" ref="BX5">SUMPRODUCT((D5:BW5=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3318,7 +3073,7 @@
       </c>
       <c r="BX6" s="5" cm="1">
         <f t="array" ref="BX6">SUMPRODUCT((D6:BW6=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3788,7 +3543,7 @@
       </c>
       <c r="BX8" s="5" cm="1">
         <f t="array" ref="BX8">SUMPRODUCT((D8:BW8=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4258,7 +4013,7 @@
       </c>
       <c r="BX10" s="5" cm="1">
         <f t="array" ref="BX10">SUMPRODUCT((D10:BW10=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4493,7 +4248,7 @@
       </c>
       <c r="BX11" s="5" cm="1">
         <f t="array" ref="BX11">SUMPRODUCT((D11:BW11=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4728,7 +4483,7 @@
       </c>
       <c r="BX12" s="5" cm="1">
         <f t="array" ref="BX12">SUMPRODUCT((D12:BW12=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5198,7 +4953,7 @@
       </c>
       <c r="BX14" s="5" cm="1">
         <f t="array" ref="BX14">SUMPRODUCT((D14:BW14=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5668,7 +5423,7 @@
       </c>
       <c r="BX16" s="5" cm="1">
         <f t="array" ref="BX16">SUMPRODUCT((D16:BW16=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY16" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6138,7 +5893,7 @@
       </c>
       <c r="BX18" s="5" cm="1">
         <f t="array" ref="BX18">SUMPRODUCT((D18:BW18=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY18" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6373,7 +6128,7 @@
       </c>
       <c r="BX19" s="5" cm="1">
         <f t="array" ref="BX19">SUMPRODUCT((D19:BW19=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY19" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6465,6 +6220,9 @@
       <c r="AP21" s="6" t="s">
         <v>81</v>
       </c>
+      <c r="AQ21" s="6" t="s">
+        <v>94</v>
+      </c>
       <c r="AT21" s="6" t="s">
         <v>81</v>
       </c>
@@ -6504,201 +6262,206 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D19">
-    <cfRule type="cellIs" dxfId="76" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="44" operator="equal">
       <formula>$D$21</formula>
     </cfRule>
-    <cfRule type="expression" priority="42">
+    <cfRule type="expression" priority="43">
       <formula>$D$22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E19">
-    <cfRule type="cellIs" dxfId="75" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="42" operator="equal">
       <formula>$E$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F19">
-    <cfRule type="cellIs" dxfId="74" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="41" operator="equal">
       <formula>$F$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G19">
-    <cfRule type="cellIs" dxfId="73" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="40" operator="equal">
       <formula>$G$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J19">
-    <cfRule type="cellIs" dxfId="72" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="39" operator="equal">
       <formula>$J$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K19">
-    <cfRule type="cellIs" dxfId="71" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="38" operator="equal">
       <formula>$K$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L19">
-    <cfRule type="cellIs" dxfId="70" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="37" operator="equal">
       <formula>$L$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M19">
-    <cfRule type="cellIs" dxfId="69" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="36" operator="equal">
       <formula>$M$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P19">
-    <cfRule type="cellIs" dxfId="68" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="35" operator="equal">
       <formula>$P$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q19">
-    <cfRule type="cellIs" dxfId="67" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="33" operator="equal">
       <formula>$Q$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R19">
-    <cfRule type="cellIs" dxfId="66" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="32" operator="equal">
       <formula>$R$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S19">
-    <cfRule type="cellIs" dxfId="65" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="34" operator="equal">
       <formula>$S$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V19">
-    <cfRule type="cellIs" dxfId="64" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="31" operator="equal">
       <formula>$V$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W19">
-    <cfRule type="cellIs" dxfId="63" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="30" operator="equal">
       <formula>$W$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X19">
-    <cfRule type="cellIs" dxfId="62" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="29" operator="equal">
       <formula>$X$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y19">
-    <cfRule type="cellIs" dxfId="61" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="28" operator="equal">
       <formula>$Y$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB19">
-    <cfRule type="cellIs" dxfId="60" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="25" operator="equal">
       <formula>$AB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC19">
-    <cfRule type="cellIs" dxfId="59" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="24" operator="equal">
       <formula>$AC$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD19">
-    <cfRule type="cellIs" dxfId="58" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="23" operator="equal">
       <formula>$AD$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE19">
-    <cfRule type="cellIs" dxfId="57" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="22" operator="equal">
       <formula>$AE$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH19">
-    <cfRule type="cellIs" dxfId="56" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="21" operator="equal">
       <formula>$AH$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI19">
-    <cfRule type="cellIs" dxfId="55" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="20" operator="equal">
       <formula>$AI$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ19">
-    <cfRule type="cellIs" dxfId="54" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="19" operator="equal">
       <formula>$AJ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK19">
-    <cfRule type="cellIs" dxfId="53" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="equal">
       <formula>$AK$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN19">
-    <cfRule type="cellIs" dxfId="52" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="18" operator="equal">
       <formula>$AN$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO19">
-    <cfRule type="cellIs" dxfId="51" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="17" operator="equal">
       <formula>$AO$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AP2:AP19">
+    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
+      <formula>$AP$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT19">
-    <cfRule type="cellIs" dxfId="50" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="16" operator="equal">
       <formula>$AT$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU19">
-    <cfRule type="cellIs" dxfId="49" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="15" operator="equal">
       <formula>$AU$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV19">
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="4" operator="equal">
       <formula>$AV$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AW2:AW19">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+      <formula>$AW$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ19">
-    <cfRule type="cellIs" dxfId="47" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="14" operator="equal">
       <formula>$AZ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA19">
-    <cfRule type="cellIs" dxfId="46" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="12" operator="equal">
       <formula>$BA$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF19">
-    <cfRule type="cellIs" dxfId="45" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="11" operator="equal">
       <formula>$BF$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG19">
-    <cfRule type="cellIs" dxfId="44" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="10" operator="equal">
       <formula>$BG$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL19">
-    <cfRule type="cellIs" dxfId="43" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="9" operator="equal">
       <formula>$BL$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM19">
-    <cfRule type="cellIs" dxfId="42" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="8" operator="equal">
       <formula>$BM$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR19">
-    <cfRule type="cellIs" dxfId="41" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="7" operator="equal">
       <formula>$BR$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS19">
-    <cfRule type="cellIs" dxfId="40" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="6" operator="equal">
       <formula>$BS$21</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AW2:AW19">
-    <cfRule type="cellIs" dxfId="39" priority="2" operator="equal">
-      <formula>$AW$21</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP2:AP19">
+  <conditionalFormatting sqref="AQ2:AQ19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$AP$21</formula>
+      <formula>$AQ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Predicciones mundial 2026 (Respuestas).xlsx
+++ b/Predicciones mundial 2026 (Respuestas).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-4°1°\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B00C0CF7-0DB5-46E7-95AF-474224D3C500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C745EFE0-3CF9-45CB-8A16-9A355D6BD4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="165">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -681,7 +681,315 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="85">
+  <dxfs count="129">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1302,10 +1610,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="84"/>
-      <tableStyleElement type="headerRow" dxfId="83"/>
-      <tableStyleElement type="firstRowStripe" dxfId="82"/>
-      <tableStyleElement type="secondRowStripe" dxfId="81"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="128"/>
+      <tableStyleElement type="headerRow" dxfId="127"/>
+      <tableStyleElement type="firstRowStripe" dxfId="126"/>
+      <tableStyleElement type="secondRowStripe" dxfId="125"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1397,10 +1705,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="80">
+    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="124">
       <calculatedColumnFormula array="1">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="79">
+    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="123">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2133,7 +2441,7 @@
       </c>
       <c r="BX2" s="5" cm="1">
         <f t="array" ref="BX2">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2368,7 +2676,7 @@
       </c>
       <c r="BX3" s="5" cm="1">
         <f t="array" ref="BX3">SUMPRODUCT((D3:BW3=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2603,7 +2911,7 @@
       </c>
       <c r="BX4" s="5" cm="1">
         <f t="array" ref="BX4">SUMPRODUCT((D4:BW4=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2838,7 +3146,7 @@
       </c>
       <c r="BX5" s="5" cm="1">
         <f t="array" ref="BX5">SUMPRODUCT((D5:BW5=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3073,7 +3381,7 @@
       </c>
       <c r="BX6" s="5" cm="1">
         <f t="array" ref="BX6">SUMPRODUCT((D6:BW6=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3308,7 +3616,7 @@
       </c>
       <c r="BX7" s="5" cm="1">
         <f t="array" ref="BX7">SUMPRODUCT((D7:BW7=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3543,7 +3851,7 @@
       </c>
       <c r="BX8" s="5" cm="1">
         <f t="array" ref="BX8">SUMPRODUCT((D8:BW8=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3778,7 +4086,7 @@
       </c>
       <c r="BX9" s="5" cm="1">
         <f t="array" ref="BX9">SUMPRODUCT((D9:BW9=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4013,7 +4321,7 @@
       </c>
       <c r="BX10" s="5" cm="1">
         <f t="array" ref="BX10">SUMPRODUCT((D10:BW10=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4248,7 +4556,7 @@
       </c>
       <c r="BX11" s="5" cm="1">
         <f t="array" ref="BX11">SUMPRODUCT((D11:BW11=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4483,7 +4791,7 @@
       </c>
       <c r="BX12" s="5" cm="1">
         <f t="array" ref="BX12">SUMPRODUCT((D12:BW12=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4718,7 +5026,7 @@
       </c>
       <c r="BX13" s="5" cm="1">
         <f t="array" ref="BX13">SUMPRODUCT((D13:BW13=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4953,7 +5261,7 @@
       </c>
       <c r="BX14" s="5" cm="1">
         <f t="array" ref="BX14">SUMPRODUCT((D14:BW14=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5188,7 +5496,7 @@
       </c>
       <c r="BX15" s="5" cm="1">
         <f t="array" ref="BX15">SUMPRODUCT((D15:BW15=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5423,7 +5731,7 @@
       </c>
       <c r="BX16" s="5" cm="1">
         <f t="array" ref="BX16">SUMPRODUCT((D16:BW16=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BY16" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5658,7 +5966,7 @@
       </c>
       <c r="BX17" s="5" cm="1">
         <f t="array" ref="BX17">SUMPRODUCT((D17:BW17=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BY17" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5893,7 +6201,7 @@
       </c>
       <c r="BX18" s="5" cm="1">
         <f t="array" ref="BX18">SUMPRODUCT((D18:BW18=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BY18" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6128,7 +6436,7 @@
       </c>
       <c r="BX19" s="5" cm="1">
         <f t="array" ref="BX19">SUMPRODUCT((D19:BW19=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BY19" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6241,11 +6549,17 @@
       <c r="BA21" s="6" t="s">
         <v>99</v>
       </c>
+      <c r="BB21" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="BF21" s="6" t="s">
         <v>101</v>
       </c>
       <c r="BG21" s="6" t="s">
         <v>103</v>
+      </c>
+      <c r="BH21" t="s">
+        <v>101</v>
       </c>
       <c r="BL21" s="6" t="s">
         <v>81</v>
@@ -6262,206 +6576,216 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D19">
-    <cfRule type="cellIs" dxfId="78" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="46" operator="equal">
       <formula>$D$21</formula>
     </cfRule>
-    <cfRule type="expression" priority="43">
+    <cfRule type="expression" priority="45">
       <formula>$D$22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E19">
-    <cfRule type="cellIs" dxfId="77" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="44" operator="equal">
       <formula>$E$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F19">
-    <cfRule type="cellIs" dxfId="76" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="43" operator="equal">
       <formula>$F$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G19">
-    <cfRule type="cellIs" dxfId="75" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="42" operator="equal">
       <formula>$G$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J19">
-    <cfRule type="cellIs" dxfId="74" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="41" operator="equal">
       <formula>$J$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K19">
-    <cfRule type="cellIs" dxfId="73" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="40" operator="equal">
       <formula>$K$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L19">
-    <cfRule type="cellIs" dxfId="72" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="39" operator="equal">
       <formula>$L$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M19">
-    <cfRule type="cellIs" dxfId="71" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="38" operator="equal">
       <formula>$M$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P19">
-    <cfRule type="cellIs" dxfId="70" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="37" operator="equal">
       <formula>$P$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q19">
-    <cfRule type="cellIs" dxfId="69" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="35" operator="equal">
       <formula>$Q$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R19">
-    <cfRule type="cellIs" dxfId="68" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="34" operator="equal">
       <formula>$R$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S19">
-    <cfRule type="cellIs" dxfId="67" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="36" operator="equal">
       <formula>$S$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V19">
-    <cfRule type="cellIs" dxfId="66" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="33" operator="equal">
       <formula>$V$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W19">
-    <cfRule type="cellIs" dxfId="65" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="32" operator="equal">
       <formula>$W$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X19">
-    <cfRule type="cellIs" dxfId="64" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="31" operator="equal">
       <formula>$X$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y19">
-    <cfRule type="cellIs" dxfId="63" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="30" operator="equal">
       <formula>$Y$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB19">
-    <cfRule type="cellIs" dxfId="62" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="27" operator="equal">
       <formula>$AB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC19">
-    <cfRule type="cellIs" dxfId="61" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="26" operator="equal">
       <formula>$AC$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD19">
-    <cfRule type="cellIs" dxfId="60" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="25" operator="equal">
       <formula>$AD$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE19">
-    <cfRule type="cellIs" dxfId="59" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="24" operator="equal">
       <formula>$AE$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH19">
-    <cfRule type="cellIs" dxfId="58" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="23" operator="equal">
       <formula>$AH$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI19">
-    <cfRule type="cellIs" dxfId="57" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="22" operator="equal">
       <formula>$AI$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ19">
-    <cfRule type="cellIs" dxfId="56" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="21" operator="equal">
       <formula>$AJ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK19">
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="7" operator="equal">
       <formula>$AK$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN19">
-    <cfRule type="cellIs" dxfId="54" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="20" operator="equal">
       <formula>$AN$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO19">
-    <cfRule type="cellIs" dxfId="53" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="19" operator="equal">
       <formula>$AO$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP19">
-    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="4" operator="equal">
       <formula>$AP$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AQ2:AQ19">
+    <cfRule type="cellIs" dxfId="55" priority="3" operator="equal">
+      <formula>$AQ$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT19">
-    <cfRule type="cellIs" dxfId="51" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="18" operator="equal">
       <formula>$AT$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU19">
-    <cfRule type="cellIs" dxfId="50" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="17" operator="equal">
       <formula>$AU$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV19">
-    <cfRule type="cellIs" dxfId="49" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="6" operator="equal">
       <formula>$AV$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW19">
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="5" operator="equal">
       <formula>$AW$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ19">
-    <cfRule type="cellIs" dxfId="47" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="16" operator="equal">
       <formula>$AZ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA19">
-    <cfRule type="cellIs" dxfId="46" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="14" operator="equal">
       <formula>$BA$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF19">
-    <cfRule type="cellIs" dxfId="45" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="13" operator="equal">
       <formula>$BF$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG19">
-    <cfRule type="cellIs" dxfId="44" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="12" operator="equal">
       <formula>$BG$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL19">
-    <cfRule type="cellIs" dxfId="43" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="11" operator="equal">
       <formula>$BL$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM19">
-    <cfRule type="cellIs" dxfId="42" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="10" operator="equal">
       <formula>$BM$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR19">
-    <cfRule type="cellIs" dxfId="41" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="9" operator="equal">
       <formula>$BR$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS19">
-    <cfRule type="cellIs" dxfId="40" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="8" operator="equal">
       <formula>$BS$21</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AQ2:AQ19">
+  <conditionalFormatting sqref="BH2:BH19">
+    <cfRule type="cellIs" dxfId="42" priority="2" operator="equal">
+      <formula>$BH$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB2:BB19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$AQ$21</formula>
+      <formula>$BB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Predicciones mundial 2026 (Respuestas).xlsx
+++ b/Predicciones mundial 2026 (Respuestas).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-4°1°\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C745EFE0-3CF9-45CB-8A16-9A355D6BD4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E0A98A-9219-46D0-8D4E-142F561DBD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1453" uniqueCount="165">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -681,273 +681,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="129">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="91">
     <dxf>
       <fill>
         <patternFill>
@@ -1610,10 +1344,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="128"/>
-      <tableStyleElement type="headerRow" dxfId="127"/>
-      <tableStyleElement type="firstRowStripe" dxfId="126"/>
-      <tableStyleElement type="secondRowStripe" dxfId="125"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="90"/>
+      <tableStyleElement type="headerRow" dxfId="89"/>
+      <tableStyleElement type="firstRowStripe" dxfId="88"/>
+      <tableStyleElement type="secondRowStripe" dxfId="87"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1705,10 +1439,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="124">
+    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="86">
       <calculatedColumnFormula array="1">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="123">
+    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="85">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2911,7 +2645,7 @@
       </c>
       <c r="BX4" s="5" cm="1">
         <f t="array" ref="BX4">SUMPRODUCT((D4:BW4=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3381,7 +3115,7 @@
       </c>
       <c r="BX6" s="5" cm="1">
         <f t="array" ref="BX6">SUMPRODUCT((D6:BW6=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3616,7 +3350,7 @@
       </c>
       <c r="BX7" s="5" cm="1">
         <f t="array" ref="BX7">SUMPRODUCT((D7:BW7=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4086,7 +3820,7 @@
       </c>
       <c r="BX9" s="5" cm="1">
         <f t="array" ref="BX9">SUMPRODUCT((D9:BW9=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4321,7 +4055,7 @@
       </c>
       <c r="BX10" s="5" cm="1">
         <f t="array" ref="BX10">SUMPRODUCT((D10:BW10=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4791,7 +4525,7 @@
       </c>
       <c r="BX12" s="5" cm="1">
         <f t="array" ref="BX12">SUMPRODUCT((D12:BW12=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5261,7 +4995,7 @@
       </c>
       <c r="BX14" s="5" cm="1">
         <f t="array" ref="BX14">SUMPRODUCT((D14:BW14=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5496,7 +5230,7 @@
       </c>
       <c r="BX15" s="5" cm="1">
         <f t="array" ref="BX15">SUMPRODUCT((D15:BW15=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5731,7 +5465,7 @@
       </c>
       <c r="BX16" s="5" cm="1">
         <f t="array" ref="BX16">SUMPRODUCT((D16:BW16=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY16" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5966,7 +5700,7 @@
       </c>
       <c r="BX17" s="5" cm="1">
         <f t="array" ref="BX17">SUMPRODUCT((D17:BW17=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY17" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6552,6 +6286,9 @@
       <c r="BB21" s="6" t="s">
         <v>98</v>
       </c>
+      <c r="BC21" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="BF21" s="6" t="s">
         <v>101</v>
       </c>
@@ -6576,216 +6313,221 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D19">
-    <cfRule type="cellIs" dxfId="82" priority="46" operator="equal">
+    <cfRule type="expression" priority="46">
+      <formula>$D$22</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="84" priority="47" operator="equal">
       <formula>$D$21</formula>
-    </cfRule>
-    <cfRule type="expression" priority="45">
-      <formula>$D$22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E19">
-    <cfRule type="cellIs" dxfId="81" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="45" operator="equal">
       <formula>$E$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F19">
-    <cfRule type="cellIs" dxfId="80" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="44" operator="equal">
       <formula>$F$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G19">
-    <cfRule type="cellIs" dxfId="79" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="43" operator="equal">
       <formula>$G$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J19">
-    <cfRule type="cellIs" dxfId="78" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="42" operator="equal">
       <formula>$J$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K19">
-    <cfRule type="cellIs" dxfId="77" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="41" operator="equal">
       <formula>$K$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L19">
-    <cfRule type="cellIs" dxfId="76" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="40" operator="equal">
       <formula>$L$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M19">
-    <cfRule type="cellIs" dxfId="75" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="39" operator="equal">
       <formula>$M$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P19">
-    <cfRule type="cellIs" dxfId="74" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="38" operator="equal">
       <formula>$P$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q19">
-    <cfRule type="cellIs" dxfId="73" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="36" operator="equal">
       <formula>$Q$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R19">
-    <cfRule type="cellIs" dxfId="72" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="35" operator="equal">
       <formula>$R$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S19">
-    <cfRule type="cellIs" dxfId="71" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="37" operator="equal">
       <formula>$S$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V19">
-    <cfRule type="cellIs" dxfId="70" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="34" operator="equal">
       <formula>$V$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W19">
-    <cfRule type="cellIs" dxfId="69" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="33" operator="equal">
       <formula>$W$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X19">
-    <cfRule type="cellIs" dxfId="68" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="32" operator="equal">
       <formula>$X$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y19">
-    <cfRule type="cellIs" dxfId="67" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="31" operator="equal">
       <formula>$Y$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB19">
-    <cfRule type="cellIs" dxfId="66" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="28" operator="equal">
       <formula>$AB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC19">
-    <cfRule type="cellIs" dxfId="65" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="27" operator="equal">
       <formula>$AC$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD19">
-    <cfRule type="cellIs" dxfId="64" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="26" operator="equal">
       <formula>$AD$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE19">
-    <cfRule type="cellIs" dxfId="63" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="25" operator="equal">
       <formula>$AE$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH19">
-    <cfRule type="cellIs" dxfId="62" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="24" operator="equal">
       <formula>$AH$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI19">
-    <cfRule type="cellIs" dxfId="61" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="23" operator="equal">
       <formula>$AI$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ19">
-    <cfRule type="cellIs" dxfId="60" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="22" operator="equal">
       <formula>$AJ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK19">
-    <cfRule type="cellIs" dxfId="59" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="8" operator="equal">
       <formula>$AK$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN19">
-    <cfRule type="cellIs" dxfId="58" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="21" operator="equal">
       <formula>$AN$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO19">
-    <cfRule type="cellIs" dxfId="57" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="20" operator="equal">
       <formula>$AO$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP19">
-    <cfRule type="cellIs" dxfId="56" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="5" operator="equal">
       <formula>$AP$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ19">
-    <cfRule type="cellIs" dxfId="55" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="4" operator="equal">
       <formula>$AQ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT19">
-    <cfRule type="cellIs" dxfId="54" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="19" operator="equal">
       <formula>$AT$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU19">
-    <cfRule type="cellIs" dxfId="53" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="18" operator="equal">
       <formula>$AU$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV19">
-    <cfRule type="cellIs" dxfId="52" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="7" operator="equal">
       <formula>$AV$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW19">
-    <cfRule type="cellIs" dxfId="51" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="6" operator="equal">
       <formula>$AW$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ19">
-    <cfRule type="cellIs" dxfId="50" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="17" operator="equal">
       <formula>$AZ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA19">
-    <cfRule type="cellIs" dxfId="49" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="15" operator="equal">
       <formula>$BA$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="BB2:BB19">
+    <cfRule type="cellIs" dxfId="50" priority="2" operator="equal">
+      <formula>$BB$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF19">
-    <cfRule type="cellIs" dxfId="48" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="14" operator="equal">
       <formula>$BF$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG19">
-    <cfRule type="cellIs" dxfId="47" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="13" operator="equal">
       <formula>$BG$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="BH2:BH19">
+    <cfRule type="cellIs" dxfId="47" priority="3" operator="equal">
+      <formula>$BH$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL19">
-    <cfRule type="cellIs" dxfId="46" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="12" operator="equal">
       <formula>$BL$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM19">
-    <cfRule type="cellIs" dxfId="45" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="11" operator="equal">
       <formula>$BM$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR19">
-    <cfRule type="cellIs" dxfId="44" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="10" operator="equal">
       <formula>$BR$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS19">
-    <cfRule type="cellIs" dxfId="43" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="9" operator="equal">
       <formula>$BS$21</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BH2:BH19">
-    <cfRule type="cellIs" dxfId="42" priority="2" operator="equal">
-      <formula>$BH$21</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BB2:BB19">
+  <conditionalFormatting sqref="BC2:BC19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$BB$21</formula>
+      <formula>$BC$21</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Predicciones mundial 2026 (Respuestas).xlsx
+++ b/Predicciones mundial 2026 (Respuestas).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-4°1°\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E0A98A-9219-46D0-8D4E-142F561DBD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD475FE-57C1-4CB4-A798-33E1F50D518C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1453" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="165">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -681,7 +681,987 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="91">
+  <dxfs count="231">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1344,10 +2324,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="90"/>
-      <tableStyleElement type="headerRow" dxfId="89"/>
-      <tableStyleElement type="firstRowStripe" dxfId="88"/>
-      <tableStyleElement type="secondRowStripe" dxfId="87"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="230"/>
+      <tableStyleElement type="headerRow" dxfId="229"/>
+      <tableStyleElement type="firstRowStripe" dxfId="228"/>
+      <tableStyleElement type="secondRowStripe" dxfId="227"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1439,10 +2419,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="86">
+    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="226">
       <calculatedColumnFormula array="1">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="85">
+    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="225">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2175,7 +3155,7 @@
       </c>
       <c r="BX2" s="5" cm="1">
         <f t="array" ref="BX2">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2410,7 +3390,7 @@
       </c>
       <c r="BX3" s="5" cm="1">
         <f t="array" ref="BX3">SUMPRODUCT((D3:BW3=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2645,7 +3625,7 @@
       </c>
       <c r="BX4" s="5" cm="1">
         <f t="array" ref="BX4">SUMPRODUCT((D4:BW4=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2880,7 +3860,7 @@
       </c>
       <c r="BX5" s="5" cm="1">
         <f t="array" ref="BX5">SUMPRODUCT((D5:BW5=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3115,7 +4095,7 @@
       </c>
       <c r="BX6" s="5" cm="1">
         <f t="array" ref="BX6">SUMPRODUCT((D6:BW6=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3350,7 +4330,7 @@
       </c>
       <c r="BX7" s="5" cm="1">
         <f t="array" ref="BX7">SUMPRODUCT((D7:BW7=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3585,7 +4565,7 @@
       </c>
       <c r="BX8" s="5" cm="1">
         <f t="array" ref="BX8">SUMPRODUCT((D8:BW8=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3820,7 +4800,7 @@
       </c>
       <c r="BX9" s="5" cm="1">
         <f t="array" ref="BX9">SUMPRODUCT((D9:BW9=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4055,7 +5035,7 @@
       </c>
       <c r="BX10" s="5" cm="1">
         <f t="array" ref="BX10">SUMPRODUCT((D10:BW10=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4290,7 +5270,7 @@
       </c>
       <c r="BX11" s="5" cm="1">
         <f t="array" ref="BX11">SUMPRODUCT((D11:BW11=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4525,7 +5505,7 @@
       </c>
       <c r="BX12" s="5" cm="1">
         <f t="array" ref="BX12">SUMPRODUCT((D12:BW12=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4760,7 +5740,7 @@
       </c>
       <c r="BX13" s="5" cm="1">
         <f t="array" ref="BX13">SUMPRODUCT((D13:BW13=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4995,7 +5975,7 @@
       </c>
       <c r="BX14" s="5" cm="1">
         <f t="array" ref="BX14">SUMPRODUCT((D14:BW14=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5230,7 +6210,7 @@
       </c>
       <c r="BX15" s="5" cm="1">
         <f t="array" ref="BX15">SUMPRODUCT((D15:BW15=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5465,7 +6445,7 @@
       </c>
       <c r="BX16" s="5" cm="1">
         <f t="array" ref="BX16">SUMPRODUCT((D16:BW16=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BY16" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5700,7 +6680,7 @@
       </c>
       <c r="BX17" s="5" cm="1">
         <f t="array" ref="BX17">SUMPRODUCT((D17:BW17=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BY17" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5935,7 +6915,7 @@
       </c>
       <c r="BX18" s="5" cm="1">
         <f t="array" ref="BX18">SUMPRODUCT((D18:BW18=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BY18" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6170,7 +7150,7 @@
       </c>
       <c r="BX19" s="5" cm="1">
         <f t="array" ref="BX19">SUMPRODUCT((D19:BW19=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BY19" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6298,236 +7278,268 @@
       <c r="BH21" t="s">
         <v>101</v>
       </c>
+      <c r="BI21" t="s">
+        <v>119</v>
+      </c>
       <c r="BL21" s="6" t="s">
         <v>81</v>
       </c>
       <c r="BM21" s="6" t="s">
         <v>105</v>
       </c>
+      <c r="BN21" s="6" t="s">
+        <v>104</v>
+      </c>
       <c r="BR21" s="6" t="s">
         <v>107</v>
       </c>
       <c r="BS21" s="6" t="s">
         <v>108</v>
+      </c>
+      <c r="BT21" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="BU21" s="6" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D19">
-    <cfRule type="expression" priority="46">
+    <cfRule type="expression" priority="50">
       <formula>$D$22</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="51" operator="equal">
       <formula>$D$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E19">
-    <cfRule type="cellIs" dxfId="83" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="49" operator="equal">
       <formula>$E$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F19">
-    <cfRule type="cellIs" dxfId="82" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="48" operator="equal">
       <formula>$F$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G19">
-    <cfRule type="cellIs" dxfId="81" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="47" operator="equal">
       <formula>$G$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J19">
-    <cfRule type="cellIs" dxfId="80" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="46" operator="equal">
       <formula>$J$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K19">
-    <cfRule type="cellIs" dxfId="79" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="45" operator="equal">
       <formula>$K$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L19">
-    <cfRule type="cellIs" dxfId="78" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="44" operator="equal">
       <formula>$L$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M19">
-    <cfRule type="cellIs" dxfId="77" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="43" operator="equal">
       <formula>$M$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P19">
-    <cfRule type="cellIs" dxfId="76" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="42" operator="equal">
       <formula>$P$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q19">
-    <cfRule type="cellIs" dxfId="75" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="40" operator="equal">
       <formula>$Q$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R19">
-    <cfRule type="cellIs" dxfId="74" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="39" operator="equal">
       <formula>$R$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S19">
-    <cfRule type="cellIs" dxfId="73" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="41" operator="equal">
       <formula>$S$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V19">
-    <cfRule type="cellIs" dxfId="72" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="38" operator="equal">
       <formula>$V$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W19">
-    <cfRule type="cellIs" dxfId="71" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="37" operator="equal">
       <formula>$W$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X19">
-    <cfRule type="cellIs" dxfId="70" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="36" operator="equal">
       <formula>$X$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y19">
-    <cfRule type="cellIs" dxfId="69" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="35" operator="equal">
       <formula>$Y$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB19">
-    <cfRule type="cellIs" dxfId="68" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="32" operator="equal">
       <formula>$AB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC19">
-    <cfRule type="cellIs" dxfId="67" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="31" operator="equal">
       <formula>$AC$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD19">
-    <cfRule type="cellIs" dxfId="66" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="30" operator="equal">
       <formula>$AD$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE19">
-    <cfRule type="cellIs" dxfId="65" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="29" operator="equal">
       <formula>$AE$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH19">
-    <cfRule type="cellIs" dxfId="64" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="28" operator="equal">
       <formula>$AH$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI19">
-    <cfRule type="cellIs" dxfId="63" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="27" operator="equal">
       <formula>$AI$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ19">
-    <cfRule type="cellIs" dxfId="62" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="26" operator="equal">
       <formula>$AJ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK19">
-    <cfRule type="cellIs" dxfId="61" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="12" operator="equal">
       <formula>$AK$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN19">
-    <cfRule type="cellIs" dxfId="60" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="25" operator="equal">
       <formula>$AN$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO19">
-    <cfRule type="cellIs" dxfId="59" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="24" operator="equal">
       <formula>$AO$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP19">
-    <cfRule type="cellIs" dxfId="58" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="9" operator="equal">
       <formula>$AP$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ19">
-    <cfRule type="cellIs" dxfId="57" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="8" operator="equal">
       <formula>$AQ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT19">
-    <cfRule type="cellIs" dxfId="56" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="23" operator="equal">
       <formula>$AT$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU19">
-    <cfRule type="cellIs" dxfId="55" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="22" operator="equal">
       <formula>$AU$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV19">
-    <cfRule type="cellIs" dxfId="54" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="11" operator="equal">
       <formula>$AV$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW19">
-    <cfRule type="cellIs" dxfId="53" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="10" operator="equal">
       <formula>$AW$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ19">
-    <cfRule type="cellIs" dxfId="52" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="21" operator="equal">
       <formula>$AZ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA19">
-    <cfRule type="cellIs" dxfId="51" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="19" operator="equal">
       <formula>$BA$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB2:BB19">
-    <cfRule type="cellIs" dxfId="50" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="6" operator="equal">
       <formula>$BB$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="BC2:BC19">
+    <cfRule type="cellIs" dxfId="57" priority="5" operator="equal">
+      <formula>$BC$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF19">
-    <cfRule type="cellIs" dxfId="49" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="18" operator="equal">
       <formula>$BF$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG19">
-    <cfRule type="cellIs" dxfId="48" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="17" operator="equal">
       <formula>$BG$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH2:BH19">
-    <cfRule type="cellIs" dxfId="47" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="7" operator="equal">
       <formula>$BH$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL19">
-    <cfRule type="cellIs" dxfId="46" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="16" operator="equal">
       <formula>$BL$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM19">
-    <cfRule type="cellIs" dxfId="45" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="15" operator="equal">
       <formula>$BM$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR19">
-    <cfRule type="cellIs" dxfId="44" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="14" operator="equal">
       <formula>$BR$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS19">
-    <cfRule type="cellIs" dxfId="43" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="13" operator="equal">
       <formula>$BS$21</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BC2:BC19">
+  <conditionalFormatting sqref="BI2:BI19">
+    <cfRule type="cellIs" dxfId="49" priority="4" operator="equal">
+      <formula>$BI$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BN2:BN19">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+      <formula>$BN$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BT2:BT19">
+    <cfRule type="cellIs" dxfId="47" priority="2" operator="equal">
+      <formula>$BT$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BU2:BU19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$BC$21</formula>
+      <formula>$BU$21</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Predicciones mundial 2026 (Respuestas).xlsx
+++ b/Predicciones mundial 2026 (Respuestas).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-4°1°\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD475FE-57C1-4CB4-A798-33E1F50D518C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5515B0F6-3C22-4891-BE94-CCB80B5CADB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="165">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -681,917 +681,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="231">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="101">
     <dxf>
       <fill>
         <patternFill>
@@ -2324,10 +1414,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="230"/>
-      <tableStyleElement type="headerRow" dxfId="229"/>
-      <tableStyleElement type="firstRowStripe" dxfId="228"/>
-      <tableStyleElement type="secondRowStripe" dxfId="227"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="100"/>
+      <tableStyleElement type="headerRow" dxfId="99"/>
+      <tableStyleElement type="firstRowStripe" dxfId="98"/>
+      <tableStyleElement type="secondRowStripe" dxfId="97"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2419,10 +1509,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="226">
+    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="96">
       <calculatedColumnFormula array="1">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="225">
+    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="95">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3155,7 +2245,7 @@
       </c>
       <c r="BX2" s="5" cm="1">
         <f t="array" ref="BX2">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3390,7 +2480,7 @@
       </c>
       <c r="BX3" s="5" cm="1">
         <f t="array" ref="BX3">SUMPRODUCT((D3:BW3=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3860,7 +2950,7 @@
       </c>
       <c r="BX5" s="5" cm="1">
         <f t="array" ref="BX5">SUMPRODUCT((D5:BW5=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4095,7 +3185,7 @@
       </c>
       <c r="BX6" s="5" cm="1">
         <f t="array" ref="BX6">SUMPRODUCT((D6:BW6=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4565,7 +3655,7 @@
       </c>
       <c r="BX8" s="5" cm="1">
         <f t="array" ref="BX8">SUMPRODUCT((D8:BW8=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4800,7 +3890,7 @@
       </c>
       <c r="BX9" s="5" cm="1">
         <f t="array" ref="BX9">SUMPRODUCT((D9:BW9=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5035,7 +4125,7 @@
       </c>
       <c r="BX10" s="5" cm="1">
         <f t="array" ref="BX10">SUMPRODUCT((D10:BW10=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5270,7 +4360,7 @@
       </c>
       <c r="BX11" s="5" cm="1">
         <f t="array" ref="BX11">SUMPRODUCT((D11:BW11=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5505,7 +4595,7 @@
       </c>
       <c r="BX12" s="5" cm="1">
         <f t="array" ref="BX12">SUMPRODUCT((D12:BW12=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5740,7 +4830,7 @@
       </c>
       <c r="BX13" s="5" cm="1">
         <f t="array" ref="BX13">SUMPRODUCT((D13:BW13=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5975,7 +5065,7 @@
       </c>
       <c r="BX14" s="5" cm="1">
         <f t="array" ref="BX14">SUMPRODUCT((D14:BW14=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6445,7 +5535,7 @@
       </c>
       <c r="BX16" s="5" cm="1">
         <f t="array" ref="BX16">SUMPRODUCT((D16:BW16=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY16" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6680,7 +5770,7 @@
       </c>
       <c r="BX17" s="5" cm="1">
         <f t="array" ref="BX17">SUMPRODUCT((D17:BW17=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY17" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6915,7 +6005,7 @@
       </c>
       <c r="BX18" s="5" cm="1">
         <f t="array" ref="BX18">SUMPRODUCT((D18:BW18=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY18" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7150,7 +6240,7 @@
       </c>
       <c r="BX19" s="5" cm="1">
         <f t="array" ref="BX19">SUMPRODUCT((D19:BW19=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY19" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7290,6 +6380,9 @@
       <c r="BN21" s="6" t="s">
         <v>104</v>
       </c>
+      <c r="BO21" s="6" t="s">
+        <v>105</v>
+      </c>
       <c r="BR21" s="6" t="s">
         <v>107</v>
       </c>
@@ -7305,241 +6398,246 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D19">
-    <cfRule type="expression" priority="50">
+    <cfRule type="expression" priority="51">
       <formula>$D$22</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="51" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="52" operator="equal">
       <formula>$D$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E19">
-    <cfRule type="cellIs" dxfId="91" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="50" operator="equal">
       <formula>$E$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F19">
-    <cfRule type="cellIs" dxfId="90" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="49" operator="equal">
       <formula>$F$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G19">
-    <cfRule type="cellIs" dxfId="89" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="48" operator="equal">
       <formula>$G$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J19">
-    <cfRule type="cellIs" dxfId="88" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="47" operator="equal">
       <formula>$J$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K19">
-    <cfRule type="cellIs" dxfId="87" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="46" operator="equal">
       <formula>$K$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L19">
-    <cfRule type="cellIs" dxfId="86" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="45" operator="equal">
       <formula>$L$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M19">
-    <cfRule type="cellIs" dxfId="85" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="44" operator="equal">
       <formula>$M$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P19">
-    <cfRule type="cellIs" dxfId="84" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="43" operator="equal">
       <formula>$P$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q19">
-    <cfRule type="cellIs" dxfId="83" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="41" operator="equal">
       <formula>$Q$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R19">
-    <cfRule type="cellIs" dxfId="82" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="40" operator="equal">
       <formula>$R$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S19">
-    <cfRule type="cellIs" dxfId="81" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="42" operator="equal">
       <formula>$S$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V19">
-    <cfRule type="cellIs" dxfId="80" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="39" operator="equal">
       <formula>$V$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W19">
-    <cfRule type="cellIs" dxfId="79" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="38" operator="equal">
       <formula>$W$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X19">
-    <cfRule type="cellIs" dxfId="78" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="37" operator="equal">
       <formula>$X$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y19">
-    <cfRule type="cellIs" dxfId="77" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="36" operator="equal">
       <formula>$Y$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB19">
-    <cfRule type="cellIs" dxfId="76" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="33" operator="equal">
       <formula>$AB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC19">
-    <cfRule type="cellIs" dxfId="75" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="32" operator="equal">
       <formula>$AC$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD19">
-    <cfRule type="cellIs" dxfId="74" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="31" operator="equal">
       <formula>$AD$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE19">
-    <cfRule type="cellIs" dxfId="73" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="30" operator="equal">
       <formula>$AE$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH19">
-    <cfRule type="cellIs" dxfId="72" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="29" operator="equal">
       <formula>$AH$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI19">
-    <cfRule type="cellIs" dxfId="71" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="28" operator="equal">
       <formula>$AI$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ19">
-    <cfRule type="cellIs" dxfId="70" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="27" operator="equal">
       <formula>$AJ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK19">
-    <cfRule type="cellIs" dxfId="69" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="13" operator="equal">
       <formula>$AK$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN19">
-    <cfRule type="cellIs" dxfId="68" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="26" operator="equal">
       <formula>$AN$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO19">
-    <cfRule type="cellIs" dxfId="67" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="25" operator="equal">
       <formula>$AO$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP19">
-    <cfRule type="cellIs" dxfId="66" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="10" operator="equal">
       <formula>$AP$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ19">
-    <cfRule type="cellIs" dxfId="65" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="9" operator="equal">
       <formula>$AQ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT19">
-    <cfRule type="cellIs" dxfId="64" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="24" operator="equal">
       <formula>$AT$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU19">
-    <cfRule type="cellIs" dxfId="63" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="23" operator="equal">
       <formula>$AU$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV19">
-    <cfRule type="cellIs" dxfId="62" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="12" operator="equal">
       <formula>$AV$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW19">
-    <cfRule type="cellIs" dxfId="61" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="11" operator="equal">
       <formula>$AW$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ19">
-    <cfRule type="cellIs" dxfId="60" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="22" operator="equal">
       <formula>$AZ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA19">
-    <cfRule type="cellIs" dxfId="59" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="20" operator="equal">
       <formula>$BA$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB2:BB19">
-    <cfRule type="cellIs" dxfId="58" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="7" operator="equal">
       <formula>$BB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC2:BC19">
-    <cfRule type="cellIs" dxfId="57" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="6" operator="equal">
       <formula>$BC$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF19">
-    <cfRule type="cellIs" dxfId="56" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="19" operator="equal">
       <formula>$BF$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG19">
-    <cfRule type="cellIs" dxfId="55" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="18" operator="equal">
       <formula>$BG$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH2:BH19">
-    <cfRule type="cellIs" dxfId="54" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="8" operator="equal">
       <formula>$BH$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="BI2:BI19">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="equal">
+      <formula>$BI$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL19">
-    <cfRule type="cellIs" dxfId="53" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="17" operator="equal">
       <formula>$BL$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM19">
-    <cfRule type="cellIs" dxfId="52" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="16" operator="equal">
       <formula>$BM$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="BN2:BN19">
+    <cfRule type="cellIs" dxfId="52" priority="4" operator="equal">
+      <formula>$BN$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR19">
-    <cfRule type="cellIs" dxfId="51" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="15" operator="equal">
       <formula>$BR$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS19">
-    <cfRule type="cellIs" dxfId="50" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="14" operator="equal">
       <formula>$BS$21</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BI2:BI19">
-    <cfRule type="cellIs" dxfId="49" priority="4" operator="equal">
-      <formula>$BI$21</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BN2:BN19">
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
-      <formula>$BN$21</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="BT2:BT19">
-    <cfRule type="cellIs" dxfId="47" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="3" operator="equal">
       <formula>$BT$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BU2:BU19">
+    <cfRule type="cellIs" dxfId="48" priority="2" operator="equal">
+      <formula>$BU$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BO2:BO19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$BU$21</formula>
+      <formula>$BO$21</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Predicciones mundial 2026 (Respuestas).xlsx
+++ b/Predicciones mundial 2026 (Respuestas).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-4°1°\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5515B0F6-3C22-4891-BE94-CCB80B5CADB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA7E0C8-D553-407F-B3F4-86141EDCBF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="165">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -681,7 +681,1092 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="101">
+  <dxfs count="256">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1414,10 +2499,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="100"/>
-      <tableStyleElement type="headerRow" dxfId="99"/>
-      <tableStyleElement type="firstRowStripe" dxfId="98"/>
-      <tableStyleElement type="secondRowStripe" dxfId="97"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="255"/>
+      <tableStyleElement type="headerRow" dxfId="254"/>
+      <tableStyleElement type="firstRowStripe" dxfId="253"/>
+      <tableStyleElement type="secondRowStripe" dxfId="252"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1509,10 +2594,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="96">
+    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="251">
       <calculatedColumnFormula array="1">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="95">
+    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="250">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2245,7 +3330,7 @@
       </c>
       <c r="BX2" s="5" cm="1">
         <f t="array" ref="BX2">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2480,7 +3565,7 @@
       </c>
       <c r="BX3" s="5" cm="1">
         <f t="array" ref="BX3">SUMPRODUCT((D3:BW3=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2715,7 +3800,7 @@
       </c>
       <c r="BX4" s="5" cm="1">
         <f t="array" ref="BX4">SUMPRODUCT((D4:BW4=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2950,7 +4035,7 @@
       </c>
       <c r="BX5" s="5" cm="1">
         <f t="array" ref="BX5">SUMPRODUCT((D5:BW5=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3185,7 +4270,7 @@
       </c>
       <c r="BX6" s="5" cm="1">
         <f t="array" ref="BX6">SUMPRODUCT((D6:BW6=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3420,7 +4505,7 @@
       </c>
       <c r="BX7" s="5" cm="1">
         <f t="array" ref="BX7">SUMPRODUCT((D7:BW7=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3655,7 +4740,7 @@
       </c>
       <c r="BX8" s="5" cm="1">
         <f t="array" ref="BX8">SUMPRODUCT((D8:BW8=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3890,7 +4975,7 @@
       </c>
       <c r="BX9" s="5" cm="1">
         <f t="array" ref="BX9">SUMPRODUCT((D9:BW9=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4125,7 +5210,7 @@
       </c>
       <c r="BX10" s="5" cm="1">
         <f t="array" ref="BX10">SUMPRODUCT((D10:BW10=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4360,7 +5445,7 @@
       </c>
       <c r="BX11" s="5" cm="1">
         <f t="array" ref="BX11">SUMPRODUCT((D11:BW11=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4595,7 +5680,7 @@
       </c>
       <c r="BX12" s="5" cm="1">
         <f t="array" ref="BX12">SUMPRODUCT((D12:BW12=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4830,7 +5915,7 @@
       </c>
       <c r="BX13" s="5" cm="1">
         <f t="array" ref="BX13">SUMPRODUCT((D13:BW13=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5065,7 +6150,7 @@
       </c>
       <c r="BX14" s="5" cm="1">
         <f t="array" ref="BX14">SUMPRODUCT((D14:BW14=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5300,7 +6385,7 @@
       </c>
       <c r="BX15" s="5" cm="1">
         <f t="array" ref="BX15">SUMPRODUCT((D15:BW15=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5535,7 +6620,7 @@
       </c>
       <c r="BX16" s="5" cm="1">
         <f t="array" ref="BX16">SUMPRODUCT((D16:BW16=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BY16" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5770,7 +6855,7 @@
       </c>
       <c r="BX17" s="5" cm="1">
         <f t="array" ref="BX17">SUMPRODUCT((D17:BW17=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BY17" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6005,7 +7090,7 @@
       </c>
       <c r="BX18" s="5" cm="1">
         <f t="array" ref="BX18">SUMPRODUCT((D18:BW18=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BY18" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6240,7 +7325,7 @@
       </c>
       <c r="BX19" s="5" cm="1">
         <f t="array" ref="BX19">SUMPRODUCT((D19:BW19=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="BY19" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6275,6 +7360,12 @@
       <c r="M21" s="6" t="s">
         <v>79</v>
       </c>
+      <c r="N21" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="O21" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="P21" s="6" t="s">
         <v>81</v>
       </c>
@@ -6286,6 +7377,12 @@
       </c>
       <c r="S21" s="6" t="s">
         <v>82</v>
+      </c>
+      <c r="T21" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="U21" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="V21" s="6" t="s">
         <v>116</v>
@@ -6398,246 +7495,266 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D19">
-    <cfRule type="expression" priority="51">
+    <cfRule type="expression" priority="55">
       <formula>$D$22</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="56" operator="equal">
       <formula>$D$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E19">
-    <cfRule type="cellIs" dxfId="93" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="54" operator="equal">
       <formula>$E$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F19">
-    <cfRule type="cellIs" dxfId="92" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="53" operator="equal">
       <formula>$F$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G19">
-    <cfRule type="cellIs" dxfId="91" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="52" operator="equal">
       <formula>$G$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J19">
-    <cfRule type="cellIs" dxfId="90" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="51" operator="equal">
       <formula>$J$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K19">
-    <cfRule type="cellIs" dxfId="89" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="50" operator="equal">
       <formula>$K$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L19">
-    <cfRule type="cellIs" dxfId="88" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="49" operator="equal">
       <formula>$L$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M19">
-    <cfRule type="cellIs" dxfId="87" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="48" operator="equal">
       <formula>$M$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P19">
-    <cfRule type="cellIs" dxfId="86" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="47" operator="equal">
       <formula>$P$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q19">
-    <cfRule type="cellIs" dxfId="85" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="45" operator="equal">
       <formula>$Q$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R19">
-    <cfRule type="cellIs" dxfId="84" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="44" operator="equal">
       <formula>$R$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S19">
-    <cfRule type="cellIs" dxfId="83" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="46" operator="equal">
       <formula>$S$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V19">
-    <cfRule type="cellIs" dxfId="82" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="43" operator="equal">
       <formula>$V$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W19">
-    <cfRule type="cellIs" dxfId="81" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="42" operator="equal">
       <formula>$W$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X19">
-    <cfRule type="cellIs" dxfId="80" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="41" operator="equal">
       <formula>$X$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y19">
-    <cfRule type="cellIs" dxfId="79" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="40" operator="equal">
       <formula>$Y$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB19">
-    <cfRule type="cellIs" dxfId="78" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="37" operator="equal">
       <formula>$AB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC19">
-    <cfRule type="cellIs" dxfId="77" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="36" operator="equal">
       <formula>$AC$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD19">
-    <cfRule type="cellIs" dxfId="76" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="35" operator="equal">
       <formula>$AD$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE19">
-    <cfRule type="cellIs" dxfId="75" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="34" operator="equal">
       <formula>$AE$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH19">
-    <cfRule type="cellIs" dxfId="74" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="33" operator="equal">
       <formula>$AH$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI19">
-    <cfRule type="cellIs" dxfId="73" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="32" operator="equal">
       <formula>$AI$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ19">
-    <cfRule type="cellIs" dxfId="72" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="31" operator="equal">
       <formula>$AJ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK19">
-    <cfRule type="cellIs" dxfId="71" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="17" operator="equal">
       <formula>$AK$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN19">
-    <cfRule type="cellIs" dxfId="70" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="30" operator="equal">
       <formula>$AN$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO19">
-    <cfRule type="cellIs" dxfId="69" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="29" operator="equal">
       <formula>$AO$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP19">
-    <cfRule type="cellIs" dxfId="68" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="14" operator="equal">
       <formula>$AP$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ19">
-    <cfRule type="cellIs" dxfId="67" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="13" operator="equal">
       <formula>$AQ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT19">
-    <cfRule type="cellIs" dxfId="66" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="28" operator="equal">
       <formula>$AT$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU19">
-    <cfRule type="cellIs" dxfId="65" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="27" operator="equal">
       <formula>$AU$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV19">
-    <cfRule type="cellIs" dxfId="64" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="16" operator="equal">
       <formula>$AV$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW19">
-    <cfRule type="cellIs" dxfId="63" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="15" operator="equal">
       <formula>$AW$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ19">
-    <cfRule type="cellIs" dxfId="62" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="26" operator="equal">
       <formula>$AZ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA19">
-    <cfRule type="cellIs" dxfId="61" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="24" operator="equal">
       <formula>$BA$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB2:BB19">
-    <cfRule type="cellIs" dxfId="60" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="11" operator="equal">
       <formula>$BB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC2:BC19">
-    <cfRule type="cellIs" dxfId="59" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="10" operator="equal">
       <formula>$BC$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF19">
-    <cfRule type="cellIs" dxfId="58" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="23" operator="equal">
       <formula>$BF$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG19">
-    <cfRule type="cellIs" dxfId="57" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="22" operator="equal">
       <formula>$BG$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH2:BH19">
-    <cfRule type="cellIs" dxfId="56" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="12" operator="equal">
       <formula>$BH$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI2:BI19">
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="9" operator="equal">
       <formula>$BI$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL19">
-    <cfRule type="cellIs" dxfId="54" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="21" operator="equal">
       <formula>$BL$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM19">
-    <cfRule type="cellIs" dxfId="53" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="20" operator="equal">
       <formula>$BM$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BN2:BN19">
-    <cfRule type="cellIs" dxfId="52" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="8" operator="equal">
       <formula>$BN$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="BO2:BO19">
+    <cfRule type="cellIs" dxfId="59" priority="5" operator="equal">
+      <formula>$BO$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR19">
-    <cfRule type="cellIs" dxfId="51" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="19" operator="equal">
       <formula>$BR$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS19">
-    <cfRule type="cellIs" dxfId="50" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="18" operator="equal">
       <formula>$BS$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT2:BT19">
-    <cfRule type="cellIs" dxfId="49" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="7" operator="equal">
       <formula>$BT$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BU2:BU19">
-    <cfRule type="cellIs" dxfId="48" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="6" operator="equal">
       <formula>$BU$21</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BO2:BO19">
+  <conditionalFormatting sqref="N2:N19">
+    <cfRule type="cellIs" dxfId="54" priority="4" operator="equal">
+      <formula>$N$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O19">
+    <cfRule type="cellIs" dxfId="53" priority="3" operator="equal">
+      <formula>$O$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T19">
+    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
+      <formula>$T$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U2:U19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$BO$21</formula>
+      <formula>$U$21</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Predicciones mundial 2026 (Respuestas).xlsx
+++ b/Predicciones mundial 2026 (Respuestas).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-4°1°\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA7E0C8-D553-407F-B3F4-86141EDCBF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC7B3A1-580A-4C0B-9445-CDE386C1A41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="165">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -681,7 +681,546 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="256">
+  <dxfs count="333">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2499,10 +3038,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="255"/>
-      <tableStyleElement type="headerRow" dxfId="254"/>
-      <tableStyleElement type="firstRowStripe" dxfId="253"/>
-      <tableStyleElement type="secondRowStripe" dxfId="252"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="332"/>
+      <tableStyleElement type="headerRow" dxfId="331"/>
+      <tableStyleElement type="firstRowStripe" dxfId="330"/>
+      <tableStyleElement type="secondRowStripe" dxfId="329"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2594,10 +3133,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="251">
+    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="328">
       <calculatedColumnFormula array="1">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="250">
+    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="327">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3330,7 +3869,7 @@
       </c>
       <c r="BX2" s="5" cm="1">
         <f t="array" ref="BX2">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3565,7 +4104,7 @@
       </c>
       <c r="BX3" s="5" cm="1">
         <f t="array" ref="BX3">SUMPRODUCT((D3:BW3=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3800,7 +4339,7 @@
       </c>
       <c r="BX4" s="5" cm="1">
         <f t="array" ref="BX4">SUMPRODUCT((D4:BW4=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4035,7 +4574,7 @@
       </c>
       <c r="BX5" s="5" cm="1">
         <f t="array" ref="BX5">SUMPRODUCT((D5:BW5=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4270,7 +4809,7 @@
       </c>
       <c r="BX6" s="5" cm="1">
         <f t="array" ref="BX6">SUMPRODUCT((D6:BW6=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4505,7 +5044,7 @@
       </c>
       <c r="BX7" s="5" cm="1">
         <f t="array" ref="BX7">SUMPRODUCT((D7:BW7=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4740,7 +5279,7 @@
       </c>
       <c r="BX8" s="5" cm="1">
         <f t="array" ref="BX8">SUMPRODUCT((D8:BW8=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4975,7 +5514,7 @@
       </c>
       <c r="BX9" s="5" cm="1">
         <f t="array" ref="BX9">SUMPRODUCT((D9:BW9=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5210,7 +5749,7 @@
       </c>
       <c r="BX10" s="5" cm="1">
         <f t="array" ref="BX10">SUMPRODUCT((D10:BW10=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5445,7 +5984,7 @@
       </c>
       <c r="BX11" s="5" cm="1">
         <f t="array" ref="BX11">SUMPRODUCT((D11:BW11=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5680,7 +6219,7 @@
       </c>
       <c r="BX12" s="5" cm="1">
         <f t="array" ref="BX12">SUMPRODUCT((D12:BW12=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5915,7 +6454,7 @@
       </c>
       <c r="BX13" s="5" cm="1">
         <f t="array" ref="BX13">SUMPRODUCT((D13:BW13=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6150,7 +6689,7 @@
       </c>
       <c r="BX14" s="5" cm="1">
         <f t="array" ref="BX14">SUMPRODUCT((D14:BW14=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6385,7 +6924,7 @@
       </c>
       <c r="BX15" s="5" cm="1">
         <f t="array" ref="BX15">SUMPRODUCT((D15:BW15=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6620,7 +7159,7 @@
       </c>
       <c r="BX16" s="5" cm="1">
         <f t="array" ref="BX16">SUMPRODUCT((D16:BW16=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="BY16" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6855,7 +7394,7 @@
       </c>
       <c r="BX17" s="5" cm="1">
         <f t="array" ref="BX17">SUMPRODUCT((D17:BW17=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY17" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7090,7 +7629,7 @@
       </c>
       <c r="BX18" s="5" cm="1">
         <f t="array" ref="BX18">SUMPRODUCT((D18:BW18=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="BY18" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7325,7 +7864,7 @@
       </c>
       <c r="BX19" s="5" cm="1">
         <f t="array" ref="BX19">SUMPRODUCT((D19:BW19=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BY19" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7348,6 +7887,12 @@
       <c r="G21" s="6" t="s">
         <v>112</v>
       </c>
+      <c r="H21" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>113</v>
+      </c>
       <c r="J21" s="6" t="s">
         <v>81</v>
       </c>
@@ -7408,6 +7953,12 @@
       <c r="AE21" s="6" t="s">
         <v>81</v>
       </c>
+      <c r="AF21" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG21" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="AH21" s="6" t="s">
         <v>81</v>
       </c>
@@ -7419,6 +7970,12 @@
       </c>
       <c r="AK21" s="6" t="s">
         <v>92</v>
+      </c>
+      <c r="AL21" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM21" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="AN21" s="6" t="s">
         <v>81</v>
@@ -7495,266 +8052,291 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D19">
-    <cfRule type="expression" priority="55">
+    <cfRule type="cellIs" dxfId="112" priority="61" operator="equal">
+      <formula>$D$21</formula>
+    </cfRule>
+    <cfRule type="expression" priority="60">
       <formula>$D$22</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="56" operator="equal">
-      <formula>$D$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E19">
-    <cfRule type="cellIs" dxfId="101" priority="54" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="59" operator="equal">
       <formula>$E$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F19">
-    <cfRule type="cellIs" dxfId="100" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="58" operator="equal">
       <formula>$F$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G19">
-    <cfRule type="cellIs" dxfId="99" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="57" operator="equal">
       <formula>$G$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J19">
-    <cfRule type="cellIs" dxfId="98" priority="51" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="56" operator="equal">
       <formula>$J$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K19">
-    <cfRule type="cellIs" dxfId="97" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="55" operator="equal">
       <formula>$K$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L19">
-    <cfRule type="cellIs" dxfId="96" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="54" operator="equal">
       <formula>$L$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M19">
-    <cfRule type="cellIs" dxfId="95" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="53" operator="equal">
       <formula>$M$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N19">
+    <cfRule type="cellIs" dxfId="104" priority="9" operator="equal">
+      <formula>$N$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O19">
+    <cfRule type="cellIs" dxfId="103" priority="8" operator="equal">
+      <formula>$O$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="P2:P19">
-    <cfRule type="cellIs" dxfId="94" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="52" operator="equal">
       <formula>$P$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q19">
-    <cfRule type="cellIs" dxfId="93" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="50" operator="equal">
       <formula>$Q$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R19">
-    <cfRule type="cellIs" dxfId="92" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="49" operator="equal">
       <formula>$R$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S19">
-    <cfRule type="cellIs" dxfId="91" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="51" operator="equal">
       <formula>$S$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T19">
+    <cfRule type="cellIs" dxfId="98" priority="7" operator="equal">
+      <formula>$T$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U2:U19">
+    <cfRule type="cellIs" dxfId="97" priority="6" operator="equal">
+      <formula>$U$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="V2:V19">
-    <cfRule type="cellIs" dxfId="90" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="48" operator="equal">
       <formula>$V$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W19">
-    <cfRule type="cellIs" dxfId="89" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="47" operator="equal">
       <formula>$W$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X19">
-    <cfRule type="cellIs" dxfId="88" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="46" operator="equal">
       <formula>$X$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y19">
-    <cfRule type="cellIs" dxfId="87" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="45" operator="equal">
       <formula>$Y$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB19">
-    <cfRule type="cellIs" dxfId="86" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="42" operator="equal">
       <formula>$AB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC19">
-    <cfRule type="cellIs" dxfId="85" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="41" operator="equal">
       <formula>$AC$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD19">
-    <cfRule type="cellIs" dxfId="84" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="40" operator="equal">
       <formula>$AD$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE19">
-    <cfRule type="cellIs" dxfId="83" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="39" operator="equal">
       <formula>$AE$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH19">
-    <cfRule type="cellIs" dxfId="82" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="38" operator="equal">
       <formula>$AH$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI19">
-    <cfRule type="cellIs" dxfId="81" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="37" operator="equal">
       <formula>$AI$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ19">
-    <cfRule type="cellIs" dxfId="80" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="36" operator="equal">
       <formula>$AJ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK19">
-    <cfRule type="cellIs" dxfId="79" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="22" operator="equal">
       <formula>$AK$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN19">
-    <cfRule type="cellIs" dxfId="78" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="35" operator="equal">
       <formula>$AN$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO19">
-    <cfRule type="cellIs" dxfId="77" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="34" operator="equal">
       <formula>$AO$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP19">
-    <cfRule type="cellIs" dxfId="76" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="19" operator="equal">
       <formula>$AP$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ19">
-    <cfRule type="cellIs" dxfId="75" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="18" operator="equal">
       <formula>$AQ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT19">
-    <cfRule type="cellIs" dxfId="74" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="33" operator="equal">
       <formula>$AT$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU19">
-    <cfRule type="cellIs" dxfId="73" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="32" operator="equal">
       <formula>$AU$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV19">
-    <cfRule type="cellIs" dxfId="72" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="21" operator="equal">
       <formula>$AV$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW19">
-    <cfRule type="cellIs" dxfId="71" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="20" operator="equal">
       <formula>$AW$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ19">
-    <cfRule type="cellIs" dxfId="70" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="31" operator="equal">
       <formula>$AZ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA19">
-    <cfRule type="cellIs" dxfId="69" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="29" operator="equal">
       <formula>$BA$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB2:BB19">
-    <cfRule type="cellIs" dxfId="68" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="16" operator="equal">
       <formula>$BB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC2:BC19">
-    <cfRule type="cellIs" dxfId="67" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="15" operator="equal">
       <formula>$BC$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF19">
-    <cfRule type="cellIs" dxfId="66" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="28" operator="equal">
       <formula>$BF$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG19">
-    <cfRule type="cellIs" dxfId="65" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="27" operator="equal">
       <formula>$BG$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH2:BH19">
-    <cfRule type="cellIs" dxfId="64" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="17" operator="equal">
       <formula>$BH$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI2:BI19">
-    <cfRule type="cellIs" dxfId="63" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="14" operator="equal">
       <formula>$BI$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL19">
-    <cfRule type="cellIs" dxfId="62" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="26" operator="equal">
       <formula>$BL$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM19">
-    <cfRule type="cellIs" dxfId="61" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="25" operator="equal">
       <formula>$BM$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BN2:BN19">
-    <cfRule type="cellIs" dxfId="60" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="13" operator="equal">
       <formula>$BN$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BO2:BO19">
-    <cfRule type="cellIs" dxfId="59" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="10" operator="equal">
       <formula>$BO$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR19">
-    <cfRule type="cellIs" dxfId="58" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="24" operator="equal">
       <formula>$BR$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS19">
-    <cfRule type="cellIs" dxfId="57" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="23" operator="equal">
       <formula>$BS$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT2:BT19">
-    <cfRule type="cellIs" dxfId="56" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="12" operator="equal">
       <formula>$BT$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BU2:BU19">
-    <cfRule type="cellIs" dxfId="55" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="11" operator="equal">
       <formula>$BU$21</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N19">
-    <cfRule type="cellIs" dxfId="54" priority="4" operator="equal">
-      <formula>$N$21</formula>
+  <conditionalFormatting sqref="H2:H19">
+    <cfRule type="cellIs" dxfId="60" priority="5" operator="equal">
+      <formula>$H$21</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O19">
-    <cfRule type="cellIs" dxfId="53" priority="3" operator="equal">
-      <formula>$O$21</formula>
+  <conditionalFormatting sqref="I2:I19">
+    <cfRule type="cellIs" dxfId="59" priority="4" operator="equal">
+      <formula>$I$21</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T19">
-    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
-      <formula>$T$21</formula>
+  <conditionalFormatting sqref="AF2:AF19">
+    <cfRule type="cellIs" dxfId="58" priority="3" operator="equal">
+      <formula>$AF$21</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U19">
+  <conditionalFormatting sqref="AG2:AG19">
+    <cfRule type="cellIs" dxfId="57" priority="2" operator="equal">
+      <formula>$AG$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM2:AM19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$U$21</formula>
+      <formula>$AM$21</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Predicciones mundial 2026 (Respuestas).xlsx
+++ b/Predicciones mundial 2026 (Respuestas).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-4°1°\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC7B3A1-580A-4C0B-9445-CDE386C1A41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B4F0CA-D871-4534-A0DD-68A43FA20AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="165">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -681,1841 +681,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="333">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="71">
     <dxf>
       <fill>
         <patternFill>
@@ -3038,10 +1204,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="332"/>
-      <tableStyleElement type="headerRow" dxfId="331"/>
-      <tableStyleElement type="firstRowStripe" dxfId="330"/>
-      <tableStyleElement type="secondRowStripe" dxfId="329"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="70"/>
+      <tableStyleElement type="headerRow" dxfId="69"/>
+      <tableStyleElement type="firstRowStripe" dxfId="68"/>
+      <tableStyleElement type="secondRowStripe" dxfId="67"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3133,10 +1299,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="328">
+    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="66">
       <calculatedColumnFormula array="1">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="327">
+    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="65">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3869,7 +2035,7 @@
       </c>
       <c r="BX2" s="5" cm="1">
         <f t="array" ref="BX2">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4104,7 +2270,7 @@
       </c>
       <c r="BX3" s="5" cm="1">
         <f t="array" ref="BX3">SUMPRODUCT((D3:BW3=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4339,7 +2505,7 @@
       </c>
       <c r="BX4" s="5" cm="1">
         <f t="array" ref="BX4">SUMPRODUCT((D4:BW4=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4574,7 +2740,7 @@
       </c>
       <c r="BX5" s="5" cm="1">
         <f t="array" ref="BX5">SUMPRODUCT((D5:BW5=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4809,7 +2975,7 @@
       </c>
       <c r="BX6" s="5" cm="1">
         <f t="array" ref="BX6">SUMPRODUCT((D6:BW6=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5044,7 +3210,7 @@
       </c>
       <c r="BX7" s="5" cm="1">
         <f t="array" ref="BX7">SUMPRODUCT((D7:BW7=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5279,7 +3445,7 @@
       </c>
       <c r="BX8" s="5" cm="1">
         <f t="array" ref="BX8">SUMPRODUCT((D8:BW8=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5514,7 +3680,7 @@
       </c>
       <c r="BX9" s="5" cm="1">
         <f t="array" ref="BX9">SUMPRODUCT((D9:BW9=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5749,7 +3915,7 @@
       </c>
       <c r="BX10" s="5" cm="1">
         <f t="array" ref="BX10">SUMPRODUCT((D10:BW10=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5984,7 +4150,7 @@
       </c>
       <c r="BX11" s="5" cm="1">
         <f t="array" ref="BX11">SUMPRODUCT((D11:BW11=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6219,7 +4385,7 @@
       </c>
       <c r="BX12" s="5" cm="1">
         <f t="array" ref="BX12">SUMPRODUCT((D12:BW12=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6454,7 +4620,7 @@
       </c>
       <c r="BX13" s="5" cm="1">
         <f t="array" ref="BX13">SUMPRODUCT((D13:BW13=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6689,7 +4855,7 @@
       </c>
       <c r="BX14" s="5" cm="1">
         <f t="array" ref="BX14">SUMPRODUCT((D14:BW14=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6924,7 +5090,7 @@
       </c>
       <c r="BX15" s="5" cm="1">
         <f t="array" ref="BX15">SUMPRODUCT((D15:BW15=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7159,7 +5325,7 @@
       </c>
       <c r="BX16" s="5" cm="1">
         <f t="array" ref="BX16">SUMPRODUCT((D16:BW16=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="BY16" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7394,7 +5560,7 @@
       </c>
       <c r="BX17" s="5" cm="1">
         <f t="array" ref="BX17">SUMPRODUCT((D17:BW17=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BY17" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7629,7 +5795,7 @@
       </c>
       <c r="BX18" s="5" cm="1">
         <f t="array" ref="BX18">SUMPRODUCT((D18:BW18=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="BY18" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7864,7 +6030,7 @@
       </c>
       <c r="BX19" s="5" cm="1">
         <f t="array" ref="BX19">SUMPRODUCT((D19:BW19=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="BY19" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7941,6 +6107,12 @@
       <c r="Y21" s="6" t="s">
         <v>84</v>
       </c>
+      <c r="Z21" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA21" s="6" t="s">
+        <v>81</v>
+      </c>
       <c r="AB21" s="6" t="s">
         <v>88</v>
       </c>
@@ -7989,6 +6161,12 @@
       <c r="AQ21" s="6" t="s">
         <v>94</v>
       </c>
+      <c r="AR21" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="AS21" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="AT21" s="6" t="s">
         <v>81</v>
       </c>
@@ -8001,6 +6179,12 @@
       <c r="AW21" t="s">
         <v>81</v>
       </c>
+      <c r="AX21" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="AY21" s="6" t="s">
+        <v>95</v>
+      </c>
       <c r="AZ21" s="6" t="s">
         <v>98</v>
       </c>
@@ -8012,6 +6196,12 @@
       </c>
       <c r="BC21" s="6" t="s">
         <v>99</v>
+      </c>
+      <c r="BD21" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="BE21" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="BF21" s="6" t="s">
         <v>101</v>
@@ -8052,291 +6242,331 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D19">
-    <cfRule type="cellIs" dxfId="112" priority="61" operator="equal">
+    <cfRule type="expression" priority="68">
+      <formula>$D$22</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="69" operator="equal">
       <formula>$D$21</formula>
-    </cfRule>
-    <cfRule type="expression" priority="60">
-      <formula>$D$22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E19">
-    <cfRule type="cellIs" dxfId="111" priority="59" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="67" operator="equal">
       <formula>$E$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F19">
-    <cfRule type="cellIs" dxfId="110" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="66" operator="equal">
       <formula>$F$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G19">
-    <cfRule type="cellIs" dxfId="109" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="65" operator="equal">
       <formula>$G$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H19">
+    <cfRule type="cellIs" dxfId="60" priority="13" operator="equal">
+      <formula>$H$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I19">
+    <cfRule type="cellIs" dxfId="59" priority="12" operator="equal">
+      <formula>$I$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J2:J19">
-    <cfRule type="cellIs" dxfId="108" priority="56" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="64" operator="equal">
       <formula>$J$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K19">
-    <cfRule type="cellIs" dxfId="107" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="63" operator="equal">
       <formula>$K$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L19">
-    <cfRule type="cellIs" dxfId="106" priority="54" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="62" operator="equal">
       <formula>$L$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M19">
-    <cfRule type="cellIs" dxfId="105" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="61" operator="equal">
       <formula>$M$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N19">
-    <cfRule type="cellIs" dxfId="104" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="17" operator="equal">
       <formula>$N$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O19">
-    <cfRule type="cellIs" dxfId="103" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="16" operator="equal">
       <formula>$O$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P19">
-    <cfRule type="cellIs" dxfId="102" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="60" operator="equal">
       <formula>$P$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q19">
-    <cfRule type="cellIs" dxfId="101" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="58" operator="equal">
       <formula>$Q$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R19">
-    <cfRule type="cellIs" dxfId="100" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="57" operator="equal">
       <formula>$R$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S19">
-    <cfRule type="cellIs" dxfId="99" priority="51" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="59" operator="equal">
       <formula>$S$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T19">
-    <cfRule type="cellIs" dxfId="98" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="15" operator="equal">
       <formula>$T$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U19">
-    <cfRule type="cellIs" dxfId="97" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="14" operator="equal">
       <formula>$U$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V19">
-    <cfRule type="cellIs" dxfId="96" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="56" operator="equal">
       <formula>$V$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W19">
-    <cfRule type="cellIs" dxfId="95" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="55" operator="equal">
       <formula>$W$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X19">
-    <cfRule type="cellIs" dxfId="94" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="54" operator="equal">
       <formula>$X$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y19">
-    <cfRule type="cellIs" dxfId="93" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="53" operator="equal">
       <formula>$Y$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z19">
+    <cfRule type="cellIs" dxfId="42" priority="8" operator="equal">
+      <formula>$Z$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA19">
+    <cfRule type="cellIs" dxfId="41" priority="7" operator="equal">
+      <formula>$AA$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB19">
-    <cfRule type="cellIs" dxfId="92" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="50" operator="equal">
       <formula>$AB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC19">
-    <cfRule type="cellIs" dxfId="91" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="49" operator="equal">
       <formula>$AC$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD19">
-    <cfRule type="cellIs" dxfId="90" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="48" operator="equal">
       <formula>$AD$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE19">
-    <cfRule type="cellIs" dxfId="89" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="47" operator="equal">
       <formula>$AE$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AF2:AF19">
+    <cfRule type="cellIs" dxfId="36" priority="11" operator="equal">
+      <formula>$AF$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG2:AG19">
+    <cfRule type="cellIs" dxfId="35" priority="10" operator="equal">
+      <formula>$AG$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH19">
-    <cfRule type="cellIs" dxfId="88" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="46" operator="equal">
       <formula>$AH$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI19">
-    <cfRule type="cellIs" dxfId="87" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="45" operator="equal">
       <formula>$AI$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ19">
-    <cfRule type="cellIs" dxfId="86" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="44" operator="equal">
       <formula>$AJ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK19">
-    <cfRule type="cellIs" dxfId="85" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="30" operator="equal">
       <formula>$AK$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AM2:AM19">
+    <cfRule type="cellIs" dxfId="30" priority="9" operator="equal">
+      <formula>$AM$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN19">
-    <cfRule type="cellIs" dxfId="84" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="43" operator="equal">
       <formula>$AN$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO19">
-    <cfRule type="cellIs" dxfId="83" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="42" operator="equal">
       <formula>$AO$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP19">
-    <cfRule type="cellIs" dxfId="82" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="27" operator="equal">
       <formula>$AP$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ19">
-    <cfRule type="cellIs" dxfId="81" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="26" operator="equal">
       <formula>$AQ$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AR2:AR19">
+    <cfRule type="cellIs" dxfId="25" priority="6" operator="equal">
+      <formula>$AR$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AS2:AS19">
+    <cfRule type="cellIs" dxfId="24" priority="5" operator="equal">
+      <formula>$AS$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT19">
-    <cfRule type="cellIs" dxfId="80" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="41" operator="equal">
       <formula>$AT$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU19">
-    <cfRule type="cellIs" dxfId="79" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="40" operator="equal">
       <formula>$AU$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV19">
-    <cfRule type="cellIs" dxfId="78" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="29" operator="equal">
       <formula>$AV$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW19">
-    <cfRule type="cellIs" dxfId="77" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="28" operator="equal">
       <formula>$AW$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AX2:AX19">
+    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
+      <formula>$AX$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AY2:AY19">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+      <formula>$AY$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ19">
-    <cfRule type="cellIs" dxfId="76" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="39" operator="equal">
       <formula>$AZ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA19">
-    <cfRule type="cellIs" dxfId="75" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="37" operator="equal">
       <formula>$BA$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB2:BB19">
-    <cfRule type="cellIs" dxfId="74" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="24" operator="equal">
       <formula>$BB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC2:BC19">
-    <cfRule type="cellIs" dxfId="73" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="23" operator="equal">
       <formula>$BC$21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="BD2:BD19">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+      <formula>$BD$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BE2:BE19">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+      <formula>$BE$21</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF19">
-    <cfRule type="cellIs" dxfId="72" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="36" operator="equal">
       <formula>$BF$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG19">
-    <cfRule type="cellIs" dxfId="71" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="35" operator="equal">
       <formula>$BG$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH2:BH19">
-    <cfRule type="cellIs" dxfId="70" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="25" operator="equal">
       <formula>$BH$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI2:BI19">
-    <cfRule type="cellIs" dxfId="69" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="22" operator="equal">
       <formula>$BI$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL19">
-    <cfRule type="cellIs" dxfId="68" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="34" operator="equal">
       <formula>$BL$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM19">
-    <cfRule type="cellIs" dxfId="67" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="33" operator="equal">
       <formula>$BM$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BN2:BN19">
-    <cfRule type="cellIs" dxfId="66" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="21" operator="equal">
       <formula>$BN$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BO2:BO19">
-    <cfRule type="cellIs" dxfId="65" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="18" operator="equal">
       <formula>$BO$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR19">
-    <cfRule type="cellIs" dxfId="64" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="32" operator="equal">
       <formula>$BR$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS19">
-    <cfRule type="cellIs" dxfId="63" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="31" operator="equal">
       <formula>$BS$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT2:BT19">
-    <cfRule type="cellIs" dxfId="62" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="20" operator="equal">
       <formula>$BT$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BU2:BU19">
-    <cfRule type="cellIs" dxfId="61" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="19" operator="equal">
       <formula>$BU$21</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H19">
-    <cfRule type="cellIs" dxfId="60" priority="5" operator="equal">
-      <formula>$H$21</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I19">
-    <cfRule type="cellIs" dxfId="59" priority="4" operator="equal">
-      <formula>$I$21</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF2:AF19">
-    <cfRule type="cellIs" dxfId="58" priority="3" operator="equal">
-      <formula>$AF$21</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG2:AG19">
-    <cfRule type="cellIs" dxfId="57" priority="2" operator="equal">
-      <formula>$AG$21</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM2:AM19">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$AM$21</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Predicciones mundial 2026 (Respuestas).xlsx
+++ b/Predicciones mundial 2026 (Respuestas).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-4°1°\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B4F0CA-D871-4534-A0DD-68A43FA20AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41BA435E-29DD-4687-B939-15D8C43D1BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="165">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -681,7 +681,2884 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="71">
+  <dxfs count="482">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1204,10 +4081,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="70"/>
-      <tableStyleElement type="headerRow" dxfId="69"/>
-      <tableStyleElement type="firstRowStripe" dxfId="68"/>
-      <tableStyleElement type="secondRowStripe" dxfId="67"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="481"/>
+      <tableStyleElement type="headerRow" dxfId="480"/>
+      <tableStyleElement type="firstRowStripe" dxfId="479"/>
+      <tableStyleElement type="secondRowStripe" dxfId="478"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1299,10 +4176,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="66">
+    <tableColumn id="76" xr3:uid="{89B2BE50-115C-4295-A68A-37F41D4EE71B}" name="Puntos" dataDxfId="477">
       <calculatedColumnFormula array="1">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="65">
+    <tableColumn id="77" xr3:uid="{E179120D-2182-421C-84B3-911C858078AE}" name="Persona" dataDxfId="476">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2035,7 +4912,7 @@
       </c>
       <c r="BX2" s="5" cm="1">
         <f t="array" ref="BX2">SUMPRODUCT((D2:BW2=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2270,7 +5147,7 @@
       </c>
       <c r="BX3" s="5" cm="1">
         <f t="array" ref="BX3">SUMPRODUCT((D3:BW3=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2505,7 +5382,7 @@
       </c>
       <c r="BX4" s="5" cm="1">
         <f t="array" ref="BX4">SUMPRODUCT((D4:BW4=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2740,7 +5617,7 @@
       </c>
       <c r="BX5" s="5" cm="1">
         <f t="array" ref="BX5">SUMPRODUCT((D5:BW5=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2975,7 +5852,7 @@
       </c>
       <c r="BX6" s="5" cm="1">
         <f t="array" ref="BX6">SUMPRODUCT((D6:BW6=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3210,7 +6087,7 @@
       </c>
       <c r="BX7" s="5" cm="1">
         <f t="array" ref="BX7">SUMPRODUCT((D7:BW7=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3445,7 +6322,7 @@
       </c>
       <c r="BX8" s="5" cm="1">
         <f t="array" ref="BX8">SUMPRODUCT((D8:BW8=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3680,7 +6557,7 @@
       </c>
       <c r="BX9" s="5" cm="1">
         <f t="array" ref="BX9">SUMPRODUCT((D9:BW9=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3915,7 +6792,7 @@
       </c>
       <c r="BX10" s="5" cm="1">
         <f t="array" ref="BX10">SUMPRODUCT((D10:BW10=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4150,7 +7027,7 @@
       </c>
       <c r="BX11" s="5" cm="1">
         <f t="array" ref="BX11">SUMPRODUCT((D11:BW11=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4385,7 +7262,7 @@
       </c>
       <c r="BX12" s="5" cm="1">
         <f t="array" ref="BX12">SUMPRODUCT((D12:BW12=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4620,7 +7497,7 @@
       </c>
       <c r="BX13" s="5" cm="1">
         <f t="array" ref="BX13">SUMPRODUCT((D13:BW13=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4855,7 +7732,7 @@
       </c>
       <c r="BX14" s="5" cm="1">
         <f t="array" ref="BX14">SUMPRODUCT((D14:BW14=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5090,7 +7967,7 @@
       </c>
       <c r="BX15" s="5" cm="1">
         <f t="array" ref="BX15">SUMPRODUCT((D15:BW15=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5325,7 +8202,7 @@
       </c>
       <c r="BX16" s="5" cm="1">
         <f t="array" ref="BX16">SUMPRODUCT((D16:BW16=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="BY16" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5560,7 +8437,7 @@
       </c>
       <c r="BX17" s="5" cm="1">
         <f t="array" ref="BX17">SUMPRODUCT((D17:BW17=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY17" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5795,7 +8672,7 @@
       </c>
       <c r="BX18" s="5" cm="1">
         <f t="array" ref="BX18">SUMPRODUCT((D18:BW18=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="BY18" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6030,7 +8907,7 @@
       </c>
       <c r="BX19" s="5" cm="1">
         <f t="array" ref="BX19">SUMPRODUCT((D19:BW19=D$21:BW$21)*(D$21:BW$21&lt;&gt;""))</f>
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="BY19" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6215,6 +9092,12 @@
       <c r="BI21" t="s">
         <v>119</v>
       </c>
+      <c r="BJ21" t="s">
+        <v>81</v>
+      </c>
+      <c r="BK21" t="s">
+        <v>101</v>
+      </c>
       <c r="BL21" s="6" t="s">
         <v>81</v>
       </c>
@@ -6227,6 +9110,12 @@
       <c r="BO21" s="6" t="s">
         <v>105</v>
       </c>
+      <c r="BP21" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="BQ21" s="6" t="s">
+        <v>106</v>
+      </c>
       <c r="BR21" s="6" t="s">
         <v>107</v>
       </c>
@@ -6237,336 +9126,372 @@
         <v>81</v>
       </c>
       <c r="BU21" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="BV21" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="BW21" s="6" t="s">
         <v>109</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D19">
-    <cfRule type="expression" priority="68">
+    <cfRule type="expression" priority="74">
       <formula>$D$22</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="69" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="75" operator="equal">
       <formula>$D$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E19">
-    <cfRule type="cellIs" dxfId="63" priority="67" operator="equal">
+    <cfRule type="cellIs" dxfId="139" priority="73" operator="equal">
       <formula>$E$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F19">
-    <cfRule type="cellIs" dxfId="62" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="138" priority="72" operator="equal">
       <formula>$F$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G19">
-    <cfRule type="cellIs" dxfId="61" priority="65" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="71" operator="equal">
       <formula>$G$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H19">
-    <cfRule type="cellIs" dxfId="60" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="136" priority="19" operator="equal">
       <formula>$H$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I19">
-    <cfRule type="cellIs" dxfId="59" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="135" priority="18" operator="equal">
       <formula>$I$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J19">
-    <cfRule type="cellIs" dxfId="58" priority="64" operator="equal">
+    <cfRule type="cellIs" dxfId="134" priority="70" operator="equal">
       <formula>$J$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K19">
-    <cfRule type="cellIs" dxfId="57" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="133" priority="69" operator="equal">
       <formula>$K$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L19">
-    <cfRule type="cellIs" dxfId="56" priority="62" operator="equal">
+    <cfRule type="cellIs" dxfId="132" priority="68" operator="equal">
       <formula>$L$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M19">
-    <cfRule type="cellIs" dxfId="55" priority="61" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="67" operator="equal">
       <formula>$M$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N19">
-    <cfRule type="cellIs" dxfId="54" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="130" priority="23" operator="equal">
       <formula>$N$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O19">
-    <cfRule type="cellIs" dxfId="53" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="22" operator="equal">
       <formula>$O$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P19">
-    <cfRule type="cellIs" dxfId="52" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="128" priority="66" operator="equal">
       <formula>$P$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q19">
-    <cfRule type="cellIs" dxfId="51" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="127" priority="64" operator="equal">
       <formula>$Q$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R19">
-    <cfRule type="cellIs" dxfId="50" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="63" operator="equal">
       <formula>$R$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S19">
-    <cfRule type="cellIs" dxfId="49" priority="59" operator="equal">
+    <cfRule type="cellIs" dxfId="125" priority="65" operator="equal">
       <formula>$S$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T19">
-    <cfRule type="cellIs" dxfId="48" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="124" priority="21" operator="equal">
       <formula>$T$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U19">
-    <cfRule type="cellIs" dxfId="47" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="123" priority="20" operator="equal">
       <formula>$U$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V19">
-    <cfRule type="cellIs" dxfId="46" priority="56" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="62" operator="equal">
       <formula>$V$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W19">
-    <cfRule type="cellIs" dxfId="45" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="121" priority="61" operator="equal">
       <formula>$W$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X19">
-    <cfRule type="cellIs" dxfId="44" priority="54" operator="equal">
+    <cfRule type="cellIs" dxfId="120" priority="60" operator="equal">
       <formula>$X$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y19">
-    <cfRule type="cellIs" dxfId="43" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="59" operator="equal">
       <formula>$Y$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:Z19">
-    <cfRule type="cellIs" dxfId="42" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="118" priority="14" operator="equal">
       <formula>$Z$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA19">
-    <cfRule type="cellIs" dxfId="41" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="117" priority="13" operator="equal">
       <formula>$AA$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB19">
-    <cfRule type="cellIs" dxfId="40" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="56" operator="equal">
       <formula>$AB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC19">
-    <cfRule type="cellIs" dxfId="39" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="55" operator="equal">
       <formula>$AC$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD19">
-    <cfRule type="cellIs" dxfId="38" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="114" priority="54" operator="equal">
       <formula>$AD$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE19">
-    <cfRule type="cellIs" dxfId="37" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="53" operator="equal">
       <formula>$AE$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF2:AF19">
-    <cfRule type="cellIs" dxfId="36" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="17" operator="equal">
       <formula>$AF$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG2:AG19">
-    <cfRule type="cellIs" dxfId="35" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="16" operator="equal">
       <formula>$AG$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH19">
-    <cfRule type="cellIs" dxfId="34" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="52" operator="equal">
       <formula>$AH$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI19">
-    <cfRule type="cellIs" dxfId="33" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="51" operator="equal">
       <formula>$AI$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ19">
-    <cfRule type="cellIs" dxfId="32" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="50" operator="equal">
       <formula>$AJ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK19">
-    <cfRule type="cellIs" dxfId="31" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="36" operator="equal">
       <formula>$AK$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM2:AM19">
-    <cfRule type="cellIs" dxfId="30" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="15" operator="equal">
       <formula>$AM$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN19">
-    <cfRule type="cellIs" dxfId="29" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="49" operator="equal">
       <formula>$AN$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO19">
-    <cfRule type="cellIs" dxfId="28" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="48" operator="equal">
       <formula>$AO$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP19">
-    <cfRule type="cellIs" dxfId="27" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="33" operator="equal">
       <formula>$AP$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ19">
-    <cfRule type="cellIs" dxfId="26" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="32" operator="equal">
       <formula>$AQ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR2:AR19">
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="12" operator="equal">
       <formula>$AR$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS2:AS19">
-    <cfRule type="cellIs" dxfId="24" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="11" operator="equal">
       <formula>$AS$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT19">
-    <cfRule type="cellIs" dxfId="23" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="47" operator="equal">
       <formula>$AT$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU19">
-    <cfRule type="cellIs" dxfId="22" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="46" operator="equal">
       <formula>$AU$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV19">
-    <cfRule type="cellIs" dxfId="21" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="35" operator="equal">
       <formula>$AV$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW19">
-    <cfRule type="cellIs" dxfId="20" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="34" operator="equal">
       <formula>$AW$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AX2:AX19">
-    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="10" operator="equal">
       <formula>$AX$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AY2:AY19">
-    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="9" operator="equal">
       <formula>$AY$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ19">
-    <cfRule type="cellIs" dxfId="17" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="45" operator="equal">
       <formula>$AZ$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA19">
-    <cfRule type="cellIs" dxfId="16" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="43" operator="equal">
       <formula>$BA$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB2:BB19">
-    <cfRule type="cellIs" dxfId="15" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="30" operator="equal">
       <formula>$BB$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC2:BC19">
-    <cfRule type="cellIs" dxfId="14" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="29" operator="equal">
       <formula>$BC$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BD2:BD19">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="8" operator="equal">
       <formula>$BD$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BE2:BE19">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="7" operator="equal">
       <formula>$BE$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF19">
-    <cfRule type="cellIs" dxfId="11" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="42" operator="equal">
       <formula>$BF$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG19">
-    <cfRule type="cellIs" dxfId="10" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="41" operator="equal">
       <formula>$BG$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH2:BH19">
-    <cfRule type="cellIs" dxfId="9" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="31" operator="equal">
       <formula>$BH$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI2:BI19">
-    <cfRule type="cellIs" dxfId="8" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="28" operator="equal">
       <formula>$BI$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL19">
-    <cfRule type="cellIs" dxfId="7" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="40" operator="equal">
       <formula>$BL$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM19">
-    <cfRule type="cellIs" dxfId="6" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="39" operator="equal">
       <formula>$BM$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BN2:BN19">
-    <cfRule type="cellIs" dxfId="5" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="27" operator="equal">
       <formula>$BN$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BO2:BO19">
-    <cfRule type="cellIs" dxfId="4" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="24" operator="equal">
       <formula>$BO$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR19">
-    <cfRule type="cellIs" dxfId="3" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="38" operator="equal">
       <formula>$BR$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS19">
-    <cfRule type="cellIs" dxfId="2" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="37" operator="equal">
       <formula>$BS$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT2:BT19">
-    <cfRule type="cellIs" dxfId="1" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="26" operator="equal">
       <formula>$BT$21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BU2:BU19">
-    <cfRule type="cellIs" dxfId="0" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="25" operator="equal">
       <formula>$BU$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BJ2:BJ19">
+    <cfRule type="cellIs" dxfId="75" priority="6" operator="equal">
+      <formula>$BJ$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BK2:BK19">
+    <cfRule type="cellIs" dxfId="74" priority="5" operator="equal">
+      <formula>$BK$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BP2:BP19">
+    <cfRule type="cellIs" dxfId="73" priority="4" operator="equal">
+      <formula>$BP$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BQ2:BQ19">
+    <cfRule type="cellIs" dxfId="72" priority="3" operator="equal">
+      <formula>$BQ$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BV2:BV19">
+    <cfRule type="cellIs" dxfId="71" priority="2" operator="equal">
+      <formula>$BV$21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BW2:BW19">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>$BW$21</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
